--- a/data/vessels/2026-10-15.xlsx
+++ b/data/vessels/2026-10-15.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="426855" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B2C7E56-012F-4DA8-9043-85281F7D29FB}"/>
+  <xr:revisionPtr revIDLastSave="427530" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D1A0873-C364-4B12-A5CC-774CBE3F4F71}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="216">
   <si>
     <t>Harbor</t>
   </si>
@@ -149,6 +149,9 @@
     <t>Hapag-Lloyd</t>
   </si>
   <si>
+    <t>In transit</t>
+  </si>
+  <si>
     <t>EB Service 2</t>
   </si>
   <si>
@@ -164,9 +167,6 @@
     <t>Talon Marine Services LLC</t>
   </si>
   <si>
-    <t>In transit</t>
-  </si>
-  <si>
     <t>CMA CGM BYBLOS</t>
   </si>
   <si>
@@ -209,6 +209,9 @@
     <t>SSA Marine</t>
   </si>
   <si>
+    <t>Waiting 2.9 days</t>
+  </si>
+  <si>
     <t>Matson - HI2</t>
   </si>
   <si>
@@ -311,6 +314,12 @@
     <t>177A</t>
   </si>
   <si>
+    <t>FP2</t>
+  </si>
+  <si>
+    <t>ONE OWL</t>
+  </si>
+  <si>
     <t>SM QINGDAO</t>
   </si>
   <si>
@@ -320,12 +329,6 @@
     <t>SM Line</t>
   </si>
   <si>
-    <t>FP2</t>
-  </si>
-  <si>
-    <t>ONE OWL</t>
-  </si>
-  <si>
     <t>PCT</t>
   </si>
   <si>
@@ -461,18 +464,18 @@
     <t>POLARIS MILA</t>
   </si>
   <si>
+    <t>ARC HONOR</t>
+  </si>
+  <si>
+    <t>ED616</t>
+  </si>
+  <si>
     <t>ARC INDEPENDENCE</t>
   </si>
   <si>
     <t>ARC</t>
   </si>
   <si>
-    <t>ARC HONOR</t>
-  </si>
-  <si>
-    <t>ED616</t>
-  </si>
-  <si>
     <t>EXPRESS ROME</t>
   </si>
   <si>
@@ -512,7 +515,7 @@
     <t>YM PLUM</t>
   </si>
   <si>
-    <t>PN12640W</t>
+    <t>PN12640E</t>
   </si>
   <si>
     <t>YM TUTORIAL</t>
@@ -536,7 +539,7 @@
     <t>ONE DURBAN</t>
   </si>
   <si>
-    <t>PN32639W</t>
+    <t>NBBT0001E</t>
   </si>
   <si>
     <t>EVER MODE</t>
@@ -566,7 +569,7 @@
     <t>ONE SYNERGY</t>
   </si>
   <si>
-    <t>FP22632B</t>
+    <t>FP22632C</t>
   </si>
   <si>
     <t>MSC SOLA</t>
@@ -575,18 +578,18 @@
     <t>UK639A</t>
   </si>
   <si>
+    <t>LAVENDER ACE</t>
+  </si>
+  <si>
+    <t>123A</t>
+  </si>
+  <si>
     <t>MORNING LUCY</t>
   </si>
   <si>
     <t>KW665</t>
   </si>
   <si>
-    <t>LAVENDER ACE</t>
-  </si>
-  <si>
-    <t>123A</t>
-  </si>
-  <si>
     <t>HYUNDAI FORWARD</t>
   </si>
   <si>
@@ -617,7 +620,7 @@
     <t>EVER SMILE</t>
   </si>
   <si>
-    <t>495-136E</t>
+    <t>495E</t>
   </si>
   <si>
     <t>SWIFT ACE</t>
@@ -635,7 +638,7 @@
     <t>ONE FANTASTIC</t>
   </si>
   <si>
-    <t>FP22633C</t>
+    <t>FP22633B</t>
   </si>
   <si>
     <t>BUDAPEST EXPRESS</t>
@@ -650,6 +653,12 @@
     <t>UK640A</t>
   </si>
   <si>
+    <t>GLOVIS LEGEND</t>
+  </si>
+  <si>
+    <t>GLOVIS TREASURE</t>
+  </si>
+  <si>
     <t>TONGALA</t>
   </si>
   <si>
@@ -659,19 +668,16 @@
     <t>Jones Stevedoring Co</t>
   </si>
   <si>
-    <t>GLOVIS LEGEND</t>
-  </si>
-  <si>
-    <t>GLOVIS TREASURE</t>
-  </si>
-  <si>
     <t>MSC SABRINA</t>
   </si>
   <si>
+    <t>MC638A</t>
+  </si>
+  <si>
     <t>CORNEILLE</t>
   </si>
   <si>
-    <t>PN12642W</t>
+    <t>OILT0014E</t>
   </si>
   <si>
     <t>WESTWOOD COLUMBIA</t>
@@ -1282,7 +1288,7 @@
         <v>46310.75</v>
       </c>
       <c r="L5" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1293,19 +1299,19 @@
         <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I6" t="s">
         <v>18</v>
@@ -1317,7 +1323,7 @@
         <v>46311.708333333336</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1387,7 +1393,7 @@
         <v>46312.291666666664</v>
       </c>
       <c r="L8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1425,7 +1431,7 @@
         <v>46311.916666666664</v>
       </c>
       <c r="L9" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1436,10 +1442,10 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F10" t="s">
         <v>54</v>
@@ -1460,7 +1466,7 @@
         <v>46312.125</v>
       </c>
       <c r="L10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1474,13 +1480,13 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G11" t="s">
         <v>17</v>
@@ -1489,7 +1495,7 @@
         <v>55</v>
       </c>
       <c r="I11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J11" s="2">
         <v>46311.541666666664</v>
@@ -1509,16 +1515,16 @@
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G12" t="s">
         <v>28</v>
@@ -1536,7 +1542,7 @@
         <v>46312.708333333336</v>
       </c>
       <c r="L12" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1544,28 +1550,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E13" s="1">
         <v>26164</v>
       </c>
       <c r="F13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J13" s="2">
         <v>46311.625</v>
@@ -1585,16 +1591,16 @@
         <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G14" t="s">
         <v>28</v>
@@ -1612,7 +1618,7 @@
         <v>46312.708333333336</v>
       </c>
       <c r="L14" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1626,13 +1632,13 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G15" t="s">
         <v>17</v>
@@ -1641,7 +1647,7 @@
         <v>55</v>
       </c>
       <c r="I15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J15" s="2">
         <v>46312.125</v>
@@ -1658,19 +1664,19 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G16" t="s">
         <v>17</v>
@@ -1685,7 +1691,7 @@
         <v>46314.75</v>
       </c>
       <c r="L16" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1696,13 +1702,13 @@
         <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F17" t="s">
         <v>44</v>
@@ -1720,7 +1726,7 @@
         <v>46314.791666666664</v>
       </c>
       <c r="L17" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1731,19 +1737,19 @@
         <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I18" t="s">
         <v>18</v>
@@ -1755,7 +1761,7 @@
         <v>46313.75</v>
       </c>
       <c r="L18" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1769,13 +1775,13 @@
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s">
         <v>17</v>
@@ -1804,13 +1810,13 @@
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G20" t="s">
         <v>17</v>
@@ -1830,26 +1836,26 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>73</v>
+      </c>
+      <c r="C21" t="s">
+        <v>91</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="E21" s="1">
+        <v>34</v>
       </c>
       <c r="F21" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="G21" t="s">
         <v>17</v>
       </c>
-      <c r="H21" t="s">
-        <v>55</v>
-      </c>
       <c r="I21" t="s">
         <v>18</v>
       </c>
@@ -1857,34 +1863,34 @@
         <v>46314.625</v>
       </c>
       <c r="K21" s="2">
-        <v>46315.166666666664</v>
+        <v>46318.75</v>
       </c>
       <c r="L21" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
         <v>93</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E22" s="1">
-        <v>34</v>
-      </c>
       <c r="F22" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="G22" t="s">
         <v>17</v>
       </c>
+      <c r="H22" t="s">
+        <v>55</v>
+      </c>
       <c r="I22" t="s">
         <v>18</v>
       </c>
@@ -1892,10 +1898,10 @@
         <v>46314.625</v>
       </c>
       <c r="K22" s="2">
-        <v>46318.75</v>
+        <v>46315.166666666664</v>
       </c>
       <c r="L22" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1903,22 +1909,22 @@
         <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G23" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I23" t="s">
         <v>18</v>
@@ -1930,7 +1936,7 @@
         <v>46316.791666666664</v>
       </c>
       <c r="L23" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1941,16 +1947,16 @@
         <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G24" t="s">
         <v>28</v>
@@ -1965,7 +1971,7 @@
         <v>46317.166666666664</v>
       </c>
       <c r="L24" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1976,13 +1982,13 @@
         <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F25" t="s">
         <v>49</v>
@@ -2000,7 +2006,7 @@
         <v>46317.75</v>
       </c>
       <c r="L25" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2014,7 +2020,7 @@
         <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -2043,19 +2049,19 @@
         <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E27" s="1">
         <v>63</v>
       </c>
       <c r="F27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G27" t="s">
         <v>28</v>
@@ -2084,10 +2090,10 @@
         <v>51</v>
       </c>
       <c r="D28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" t="s">
         <v>54</v>
@@ -2108,7 +2114,7 @@
         <v>46316.916666666664</v>
       </c>
       <c r="L28" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2116,16 +2122,16 @@
         <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D29" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F29" t="s">
         <v>35</v>
@@ -2143,7 +2149,7 @@
         <v>46319.75</v>
       </c>
       <c r="L29" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2151,34 +2157,37 @@
         <v>12</v>
       </c>
       <c r="B30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30" t="s">
+        <v>117</v>
+      </c>
+      <c r="E30" s="1">
+        <v>26169</v>
+      </c>
+      <c r="F30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30" t="s">
+        <v>71</v>
+      </c>
+      <c r="H30" t="s">
+        <v>71</v>
+      </c>
+      <c r="I30" t="s">
         <v>72</v>
-      </c>
-      <c r="C30" t="s">
-        <v>73</v>
-      </c>
-      <c r="D30" t="s">
-        <v>113</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F30" t="s">
-        <v>35</v>
-      </c>
-      <c r="G30" t="s">
-        <v>17</v>
-      </c>
-      <c r="I30" t="s">
-        <v>18</v>
       </c>
       <c r="J30" s="2">
         <v>46316.625</v>
       </c>
       <c r="K30" s="2">
-        <v>46319.75</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L30" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2186,37 +2195,34 @@
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C31" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31" t="s">
+        <v>114</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D31" t="s">
-        <v>116</v>
-      </c>
-      <c r="E31" s="1">
-        <v>26169</v>
-      </c>
       <c r="F31" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="G31" t="s">
-        <v>70</v>
-      </c>
-      <c r="H31" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="I31" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="J31" s="2">
         <v>46316.625</v>
       </c>
       <c r="K31" s="2">
-        <v>46317.041666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L31" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -2224,19 +2230,19 @@
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G32" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I32" t="s">
         <v>18</v>
@@ -2248,7 +2254,7 @@
         <v>46318.708333333336</v>
       </c>
       <c r="L32" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -2259,19 +2265,19 @@
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I33" t="s">
         <v>18</v>
@@ -2283,7 +2289,7 @@
         <v>46318.166666666664</v>
       </c>
       <c r="L33" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2297,10 +2303,10 @@
         <v>46</v>
       </c>
       <c r="D34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F34" t="s">
         <v>49</v>
@@ -2315,7 +2321,7 @@
         <v>46318.166666666664</v>
       </c>
       <c r="L34" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2329,19 +2335,19 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G35" t="s">
         <v>17</v>
       </c>
       <c r="H35" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I35" t="s">
         <v>24</v>
@@ -2364,16 +2370,16 @@
         <v>31</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D36" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F36" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I36" t="s">
         <v>18</v>
@@ -2385,7 +2391,7 @@
         <v>46318.969444444447</v>
       </c>
       <c r="L36" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -2399,7 +2405,7 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F37" t="s">
         <v>54</v>
@@ -2434,19 +2440,19 @@
         <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F38" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G38" t="s">
         <v>17</v>
       </c>
       <c r="H38" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I38" t="s">
         <v>24</v>
@@ -2472,13 +2478,13 @@
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G39" t="s">
         <v>17</v>
@@ -2504,16 +2510,16 @@
         <v>31</v>
       </c>
       <c r="C40" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D40" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G40" t="s">
         <v>28</v>
@@ -2531,7 +2537,7 @@
         <v>46319.166666666664</v>
       </c>
       <c r="L40" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2542,13 +2548,13 @@
         <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D41" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F41" t="s">
         <v>54</v>
@@ -2569,7 +2575,7 @@
         <v>46319.125</v>
       </c>
       <c r="L41" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2577,28 +2583,28 @@
         <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C42" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D42" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E42" s="1">
         <v>26168</v>
       </c>
       <c r="F42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J42" s="2">
         <v>46318.625</v>
@@ -2621,10 +2627,10 @@
         <v>51</v>
       </c>
       <c r="D43" t="s">
+        <v>139</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="F43" t="s">
         <v>54</v>
@@ -2653,7 +2659,7 @@
         <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E44" s="1">
         <v>4</v>
@@ -2682,19 +2688,19 @@
         <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>109</v>
+        <v>25</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>140</v>
-      </c>
-      <c r="E45" s="1">
-        <v>1</v>
+        <v>141</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="F45" t="s">
-        <v>141</v>
+        <v>88</v>
       </c>
       <c r="G45" t="s">
         <v>17</v>
@@ -2706,7 +2712,7 @@
         <v>46319.25</v>
       </c>
       <c r="K45" s="2">
-        <v>46322.75</v>
+        <v>46319.75</v>
       </c>
       <c r="L45" t="s">
         <v>19</v>
@@ -2717,19 +2723,19 @@
         <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>142</v>
-      </c>
-      <c r="E46" s="1" t="s">
         <v>143</v>
       </c>
+      <c r="E46" s="1">
+        <v>1</v>
+      </c>
       <c r="F46" t="s">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="G46" t="s">
         <v>17</v>
@@ -2741,7 +2747,7 @@
         <v>46319.25</v>
       </c>
       <c r="K46" s="2">
-        <v>46319.75</v>
+        <v>46322.75</v>
       </c>
       <c r="L46" t="s">
         <v>19</v>
@@ -2755,13 +2761,13 @@
         <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D47" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F47" t="s">
         <v>49</v>
@@ -2779,7 +2785,7 @@
         <v>46320.75</v>
       </c>
       <c r="L47" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2790,13 +2796,13 @@
         <v>31</v>
       </c>
       <c r="D48" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F48" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G48" t="s">
         <v>17</v>
@@ -2814,7 +2820,7 @@
         <v>46320.166666666664</v>
       </c>
       <c r="L48" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2822,19 +2828,19 @@
         <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C49" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D49" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F49" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I49" t="s">
         <v>18</v>
@@ -2846,7 +2852,7 @@
         <v>46322</v>
       </c>
       <c r="L49" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2857,13 +2863,13 @@
         <v>31</v>
       </c>
       <c r="C50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F50" t="s">
         <v>44</v>
@@ -2878,7 +2884,7 @@
         <v>46324.59375</v>
       </c>
       <c r="L50" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2889,16 +2895,16 @@
         <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D51" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F51" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G51" t="s">
         <v>28</v>
@@ -2913,7 +2919,7 @@
         <v>46323.166666666664</v>
       </c>
       <c r="L51" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -2924,13 +2930,13 @@
         <v>45</v>
       </c>
       <c r="C52" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D52" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F52" t="s">
         <v>49</v>
@@ -2945,7 +2951,7 @@
         <v>46323.21875</v>
       </c>
       <c r="L52" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -2956,16 +2962,16 @@
         <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D53" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F53" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G53" t="s">
         <v>28</v>
@@ -2980,7 +2986,7 @@
         <v>46323.166666666664</v>
       </c>
       <c r="L53" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -2988,19 +2994,19 @@
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D54" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E54" s="1">
         <v>21</v>
       </c>
       <c r="F54" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G54" t="s">
         <v>17</v>
@@ -3015,7 +3021,7 @@
         <v>46325.75</v>
       </c>
       <c r="L54" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3029,7 +3035,7 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F55" t="s">
         <v>27</v>
@@ -3058,16 +3064,16 @@
         <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C56" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D56" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F56" t="s">
         <v>35</v>
@@ -3085,7 +3091,7 @@
         <v>46325.75</v>
       </c>
       <c r="L56" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -3099,13 +3105,13 @@
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F57" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G57" t="s">
         <v>17</v>
@@ -3149,7 +3155,7 @@
         <v>46323.791666666664</v>
       </c>
       <c r="L58" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3157,28 +3163,28 @@
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C59" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D59" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E59" s="1">
         <v>26173</v>
       </c>
       <c r="F59" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G59" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H59" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I59" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J59" s="2">
         <v>46323.625</v>
@@ -3187,7 +3193,7 @@
         <v>46324.041666666664</v>
       </c>
       <c r="L59" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3198,16 +3204,16 @@
         <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D60" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F60" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I60" t="s">
         <v>18</v>
@@ -3219,7 +3225,7 @@
         <v>46327.202777777777</v>
       </c>
       <c r="L60" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3230,16 +3236,16 @@
         <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D61" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F61" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I61" t="s">
         <v>18</v>
@@ -3251,7 +3257,7 @@
         <v>46327.202777777777</v>
       </c>
       <c r="L61" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3265,13 +3271,13 @@
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F62" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G62" t="s">
         <v>17</v>
@@ -3294,16 +3300,16 @@
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D63" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F63" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I63" t="s">
         <v>18</v>
@@ -3315,7 +3321,7 @@
         <v>46326</v>
       </c>
       <c r="L63" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3329,10 +3335,10 @@
         <v>32</v>
       </c>
       <c r="D64" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F64" t="s">
         <v>44</v>
@@ -3347,7 +3353,7 @@
         <v>46326.147916666669</v>
       </c>
       <c r="L64" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3361,10 +3367,10 @@
         <v>46</v>
       </c>
       <c r="D65" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F65" t="s">
         <v>49</v>
@@ -3379,7 +3385,7 @@
         <v>46325.878472222219</v>
       </c>
       <c r="L65" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3390,16 +3396,16 @@
         <v>31</v>
       </c>
       <c r="C66" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D66" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F66" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I66" t="s">
         <v>18</v>
@@ -3411,7 +3417,7 @@
         <v>46326.098611111112</v>
       </c>
       <c r="L66" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3425,7 +3431,7 @@
         <v>51</v>
       </c>
       <c r="D67" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F67" t="s">
         <v>54</v>
@@ -3440,7 +3446,7 @@
         <v>46325.833333333336</v>
       </c>
       <c r="L67" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -3448,28 +3454,28 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C68" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D68" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E68" s="1">
         <v>26172</v>
       </c>
       <c r="F68" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G68" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H68" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I68" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J68" s="2">
         <v>46325.625</v>
@@ -3486,19 +3492,19 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D69" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F69" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I69" t="s">
         <v>18</v>
@@ -3510,7 +3516,7 @@
         <v>46329.708333333336</v>
       </c>
       <c r="L69" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3518,19 +3524,19 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C70" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F70" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I70" t="s">
         <v>18</v>
@@ -3542,7 +3548,7 @@
         <v>46329.708333333336</v>
       </c>
       <c r="L70" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3553,13 +3559,13 @@
         <v>45</v>
       </c>
       <c r="C71" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D71" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F71" t="s">
         <v>49</v>
@@ -3574,7 +3580,7 @@
         <v>46328.125</v>
       </c>
       <c r="L71" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3582,19 +3588,19 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C72" t="s">
         <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F72" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="G72" t="s">
         <v>17</v>
@@ -3617,19 +3623,19 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C73" t="s">
         <v>14</v>
       </c>
       <c r="D73" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F73" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="G73" t="s">
         <v>17</v>
@@ -3655,10 +3661,10 @@
         <v>50</v>
       </c>
       <c r="C74" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D74" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F74" t="s">
         <v>54</v>
@@ -3673,7 +3679,7 @@
         <v>46326.75</v>
       </c>
       <c r="L74" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3687,13 +3693,13 @@
         <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F75" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G75" t="s">
         <v>17</v>
@@ -3719,16 +3725,16 @@
         <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D76" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F76" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I76" t="s">
         <v>18</v>
@@ -3740,7 +3746,7 @@
         <v>46329.583333333336</v>
       </c>
       <c r="L76" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3751,10 +3757,10 @@
         <v>31</v>
       </c>
       <c r="C77" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D77" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E77" s="1">
         <v>69</v>
@@ -3772,7 +3778,7 @@
         <v>46328.541666666664</v>
       </c>
       <c r="L77" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -3786,13 +3792,13 @@
         <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F78" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G78" t="s">
         <v>17</v>
@@ -3818,10 +3824,10 @@
         <v>31</v>
       </c>
       <c r="D79" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F79" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I79" t="s">
         <v>18</v>
@@ -3833,7 +3839,7 @@
         <v>46328.833333333336</v>
       </c>
       <c r="L79" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -3844,16 +3850,16 @@
         <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D80" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F80" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I80" t="s">
         <v>18</v>
@@ -3865,7 +3871,7 @@
         <v>46331.196527777778</v>
       </c>
       <c r="L80" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3873,19 +3879,19 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C81" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D81" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F81" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I81" t="s">
         <v>18</v>
@@ -3897,7 +3903,7 @@
         <v>46330</v>
       </c>
       <c r="L81" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -3911,13 +3917,13 @@
         <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F82" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G82" t="s">
         <v>17</v>
@@ -3940,19 +3946,19 @@
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C83" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D83" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F83" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I83" t="s">
         <v>18</v>
@@ -3964,7 +3970,7 @@
         <v>46332.625</v>
       </c>
       <c r="L83" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -3978,13 +3984,13 @@
         <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F84" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G84" t="s">
         <v>17</v>
@@ -4007,19 +4013,19 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C85" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D85" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F85" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I85" t="s">
         <v>18</v>
@@ -4031,7 +4037,7 @@
         <v>46334</v>
       </c>
       <c r="L85" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4039,19 +4045,19 @@
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C86" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D86" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F86" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I86" t="s">
         <v>18</v>
@@ -4063,7 +4069,7 @@
         <v>46334</v>
       </c>
       <c r="L86" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -4071,19 +4077,19 @@
         <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C87" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D87" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F87" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I87" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J87" s="2">
         <v>46330.625</v>
@@ -4092,7 +4098,7 @@
         <v>46331.125</v>
       </c>
       <c r="L87" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4100,19 +4106,19 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C88" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D88" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F88" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I88" t="s">
         <v>18</v>
@@ -4124,7 +4130,7 @@
         <v>46333.925000000003</v>
       </c>
       <c r="L88" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4132,19 +4138,19 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C89" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D89" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F89" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I89" t="s">
         <v>18</v>
@@ -4156,7 +4162,7 @@
         <v>46333.925000000003</v>
       </c>
       <c r="L89" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4170,7 +4176,7 @@
         <v>51</v>
       </c>
       <c r="D90" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F90" t="s">
         <v>54</v>
@@ -4196,13 +4202,13 @@
         <v>45</v>
       </c>
       <c r="C91" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D91" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F91" t="s">
         <v>49</v>
@@ -4217,7 +4223,7 @@
         <v>46332.75</v>
       </c>
       <c r="L91" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4225,26 +4231,23 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C92" t="s">
         <v>14</v>
       </c>
       <c r="D92" t="s">
-        <v>203</v>
-      </c>
-      <c r="E92" s="1" t="s">
         <v>204</v>
       </c>
+      <c r="E92" s="1">
+        <v>1</v>
+      </c>
       <c r="F92" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="G92" t="s">
         <v>17</v>
       </c>
-      <c r="H92" t="s">
-        <v>205</v>
-      </c>
       <c r="I92" t="s">
         <v>24</v>
       </c>
@@ -4263,16 +4266,16 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C93" t="s">
         <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E93" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F93" t="s">
         <v>23</v>
@@ -4304,16 +4307,19 @@
         <v>14</v>
       </c>
       <c r="D94" t="s">
+        <v>206</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E94" s="1">
-        <v>10</v>
-      </c>
       <c r="F94" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="G94" t="s">
         <v>17</v>
+      </c>
+      <c r="H94" t="s">
+        <v>208</v>
       </c>
       <c r="I94" t="s">
         <v>24</v>
@@ -4339,7 +4345,10 @@
         <v>46</v>
       </c>
       <c r="D95" t="s">
-        <v>208</v>
+        <v>209</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="F95" t="s">
         <v>49</v>
@@ -4354,7 +4363,7 @@
         <v>46332.166666666664</v>
       </c>
       <c r="L95" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4365,16 +4374,16 @@
         <v>13</v>
       </c>
       <c r="C96" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D96" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F96" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I96" t="s">
         <v>18</v>
@@ -4386,7 +4395,7 @@
         <v>46334.746527777781</v>
       </c>
       <c r="L96" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4397,16 +4406,16 @@
         <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D97" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F97" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I97" t="s">
         <v>18</v>
@@ -4418,7 +4427,7 @@
         <v>46334.746527777781</v>
       </c>
       <c r="L97" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4426,26 +4435,23 @@
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C98" t="s">
         <v>14</v>
       </c>
       <c r="D98" t="s">
-        <v>203</v>
-      </c>
-      <c r="E98" s="1" t="s">
         <v>204</v>
       </c>
+      <c r="E98" s="1">
+        <v>1</v>
+      </c>
       <c r="F98" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="G98" t="s">
         <v>17</v>
       </c>
-      <c r="H98" t="s">
-        <v>205</v>
-      </c>
       <c r="I98" t="s">
         <v>24</v>
       </c>
@@ -4470,17 +4476,20 @@
         <v>14</v>
       </c>
       <c r="D99" t="s">
+        <v>206</v>
+      </c>
+      <c r="E99" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E99" s="1">
-        <v>10</v>
-      </c>
       <c r="F99" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="G99" t="s">
         <v>17</v>
       </c>
+      <c r="H99" t="s">
+        <v>208</v>
+      </c>
       <c r="I99" t="s">
         <v>24</v>
       </c>
@@ -4499,16 +4508,16 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C100" t="s">
         <v>14</v>
       </c>
       <c r="D100" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E100" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F100" t="s">
         <v>23</v>
@@ -4537,16 +4546,16 @@
         <v>31</v>
       </c>
       <c r="C101" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D101" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F101" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I101" t="s">
         <v>18</v>
@@ -4558,7 +4567,7 @@
         <v>46332.597916666666</v>
       </c>
       <c r="L101" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="102" spans="1:12">
@@ -4587,7 +4596,7 @@
         <v>46332.791666666664</v>
       </c>
       <c r="L102" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -4598,10 +4607,10 @@
         <v>31</v>
       </c>
       <c r="D103" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F103" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I103" t="s">
         <v>18</v>
@@ -4613,7 +4622,7 @@
         <v>46333.5</v>
       </c>
       <c r="L103" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="104" spans="1:12">
@@ -4624,10 +4633,10 @@
         <v>31</v>
       </c>
       <c r="D104" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F104" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I104" t="s">
         <v>18</v>
@@ -4639,7 +4648,7 @@
         <v>46333.5</v>
       </c>
       <c r="L104" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -4647,16 +4656,16 @@
         <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C105" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D105" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F105" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I105" t="s">
         <v>18</v>

--- a/data/vessels/2026-10-15.xlsx
+++ b/data/vessels/2026-10-15.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="427530" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D1A0873-C364-4B12-A5CC-774CBE3F4F71}"/>
+  <xr:revisionPtr revIDLastSave="427975" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C396799-6A5A-4A3B-ACD8-A5AF2CFAD9A4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="209">
   <si>
     <t>Harbor</t>
   </si>
@@ -77,463 +77,472 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Seattle</t>
+  </si>
+  <si>
+    <t>T18</t>
+  </si>
+  <si>
+    <t>EB Service 2</t>
+  </si>
+  <si>
+    <t>SUVA CHIEF</t>
+  </si>
+  <si>
+    <t>007E/008W</t>
+  </si>
+  <si>
+    <t>Swire</t>
+  </si>
+  <si>
+    <t>Talon Marine Services LLC</t>
+  </si>
+  <si>
+    <t>Container</t>
+  </si>
+  <si>
+    <t>In transit</t>
+  </si>
+  <si>
+    <t>Ad Hoc</t>
+  </si>
+  <si>
+    <t>CMA CGM BYBLOS</t>
+  </si>
+  <si>
+    <t>CPN00/CPN01</t>
+  </si>
+  <si>
+    <t>CMA CGM</t>
+  </si>
+  <si>
+    <t>Norton Lilly International</t>
+  </si>
+  <si>
+    <t>Not available</t>
+  </si>
+  <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>CLX</t>
+  </si>
+  <si>
+    <t>CAPE TAINARO</t>
+  </si>
+  <si>
+    <t>MC642R</t>
+  </si>
+  <si>
+    <t>MSC</t>
+  </si>
+  <si>
     <t>Tacoma</t>
   </si>
   <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>Matson - AK</t>
+  </si>
+  <si>
+    <t>MATSON KODIAK</t>
+  </si>
+  <si>
+    <t>641S</t>
+  </si>
+  <si>
+    <t>Matson</t>
+  </si>
+  <si>
+    <t>SSA Marine</t>
+  </si>
+  <si>
+    <t>Waiting 3.2 days</t>
+  </si>
+  <si>
+    <t>Matson - HI2</t>
+  </si>
+  <si>
+    <t>MANULANI</t>
+  </si>
+  <si>
+    <t>Blair</t>
+  </si>
+  <si>
+    <t>IRIS ACE</t>
+  </si>
+  <si>
+    <t>110A</t>
+  </si>
+  <si>
+    <t>ONE</t>
+  </si>
+  <si>
+    <t>Ro-Ro</t>
+  </si>
+  <si>
+    <t>PNW1</t>
+  </si>
+  <si>
+    <t>OOCL NEW YORK</t>
+  </si>
+  <si>
+    <t>122E/122W</t>
+  </si>
+  <si>
+    <t>OOCL</t>
+  </si>
+  <si>
+    <t>Inchcape</t>
+  </si>
+  <si>
+    <t>TOTE</t>
+  </si>
+  <si>
+    <t>Tote - AK2</t>
+  </si>
+  <si>
+    <t>NORTH STAR</t>
+  </si>
+  <si>
+    <t>Tote</t>
+  </si>
+  <si>
+    <t>Tote Maritime Alaska Inc</t>
+  </si>
+  <si>
+    <t>Multipurpose</t>
+  </si>
+  <si>
+    <t>EB1</t>
+  </si>
+  <si>
+    <t>Husky</t>
+  </si>
+  <si>
+    <t>WC4/TP5</t>
+  </si>
+  <si>
+    <t>MAERSK TORINO</t>
+  </si>
+  <si>
+    <t>639E/642W</t>
+  </si>
+  <si>
+    <t>Maersk</t>
+  </si>
+  <si>
+    <t>CPNW</t>
+  </si>
+  <si>
+    <t>CMA CGM ALMAVIVA</t>
+  </si>
+  <si>
+    <t>CPN02/CPN03</t>
+  </si>
+  <si>
+    <t>CPV</t>
+  </si>
+  <si>
+    <t>XIN YING KOU</t>
+  </si>
+  <si>
+    <t>269N/269S</t>
+  </si>
+  <si>
+    <t>COSCO</t>
+  </si>
+  <si>
+    <t>COSCO SHIPPING LINES</t>
+  </si>
+  <si>
+    <t>THEMISA</t>
+  </si>
+  <si>
+    <t>ED615</t>
+  </si>
+  <si>
+    <t>Wallenius</t>
+  </si>
+  <si>
+    <t>Car Carrier</t>
+  </si>
+  <si>
+    <t>SALVIA ACE</t>
+  </si>
+  <si>
+    <t>177A</t>
+  </si>
+  <si>
+    <t>FP2</t>
+  </si>
+  <si>
+    <t>ONE OWL</t>
+  </si>
+  <si>
+    <t>SM QINGDAO</t>
+  </si>
+  <si>
+    <t>2607E/2607W</t>
+  </si>
+  <si>
+    <t>SM Line</t>
+  </si>
+  <si>
+    <t>PCT</t>
+  </si>
+  <si>
+    <t>TPN</t>
+  </si>
+  <si>
+    <t>EVER ELITE</t>
+  </si>
+  <si>
+    <t>186W</t>
+  </si>
+  <si>
+    <t>Evergreen</t>
+  </si>
+  <si>
+    <t>BEN LINES</t>
+  </si>
+  <si>
     <t>WUT</t>
   </si>
   <si>
-    <t>Ad Hoc</t>
-  </si>
-  <si>
-    <t>HYUNDAI SUPREME</t>
-  </si>
-  <si>
-    <t>HMM</t>
-  </si>
-  <si>
-    <t>Norton Lilly International</t>
-  </si>
-  <si>
-    <t>Container</t>
-  </si>
-  <si>
-    <t>Not available</t>
-  </si>
-  <si>
-    <t>Blair</t>
-  </si>
-  <si>
-    <t>RCC TIANJIN</t>
-  </si>
-  <si>
-    <t>018A</t>
+    <t>PN1</t>
+  </si>
+  <si>
+    <t>YM COSMOS</t>
+  </si>
+  <si>
+    <t>PN12639W</t>
+  </si>
+  <si>
+    <t>Yang Ming</t>
+  </si>
+  <si>
+    <t>Chinook</t>
+  </si>
+  <si>
+    <t>MSC DENISSE X</t>
+  </si>
+  <si>
+    <t>UK641R</t>
+  </si>
+  <si>
+    <t>MODERN LINK</t>
   </si>
   <si>
     <t>Hyundai Glovis</t>
   </si>
   <si>
-    <t>Car Carrier</t>
-  </si>
-  <si>
-    <t>EB1</t>
-  </si>
-  <si>
-    <t>LIBERTY PRIDE</t>
+    <t>T7</t>
+  </si>
+  <si>
+    <t>THEMIS LEADER</t>
+  </si>
+  <si>
+    <t>MATSON ANCHORAGE</t>
+  </si>
+  <si>
+    <t>643S</t>
+  </si>
+  <si>
+    <t>VIENNA EXPRESS</t>
+  </si>
+  <si>
+    <t>638E/641W</t>
+  </si>
+  <si>
+    <t>Hapag-Lloyd</t>
+  </si>
+  <si>
+    <t>Tote - AK1</t>
+  </si>
+  <si>
+    <t>MIDNIGHT SUN</t>
+  </si>
+  <si>
+    <t>EVER MACH</t>
+  </si>
+  <si>
+    <t>018W</t>
+  </si>
+  <si>
+    <t>BEN LINE</t>
+  </si>
+  <si>
+    <t>COSCO VENICE</t>
+  </si>
+  <si>
+    <t>081N/081S</t>
+  </si>
+  <si>
+    <t>MSC FLORA</t>
+  </si>
+  <si>
+    <t>MC636A</t>
+  </si>
+  <si>
+    <t>ARC ENDEAVOR</t>
+  </si>
+  <si>
+    <t>A6180</t>
+  </si>
+  <si>
+    <t>Ports America Group/Pct</t>
+  </si>
+  <si>
+    <t>EB Service 1</t>
+  </si>
+  <si>
+    <t>WESTWOOD RAINIER</t>
+  </si>
+  <si>
+    <t>159E</t>
+  </si>
+  <si>
+    <t>R.J. PFEIFFER</t>
+  </si>
+  <si>
+    <t>KW664</t>
+  </si>
+  <si>
+    <t>CARNATION ACE</t>
+  </si>
+  <si>
+    <t>107A</t>
+  </si>
+  <si>
+    <t>OOCL SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>199E/199W</t>
+  </si>
+  <si>
+    <t>MAUNAWILI</t>
+  </si>
+  <si>
+    <t>642S</t>
+  </si>
+  <si>
+    <t>RJ PFEIFFER</t>
+  </si>
+  <si>
+    <t>POLARIS MILA</t>
+  </si>
+  <si>
+    <t>ARC HONOR</t>
+  </si>
+  <si>
+    <t>ED616</t>
+  </si>
+  <si>
+    <t>ARC INDEPENDENCE</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>EXPRESS ROME</t>
+  </si>
+  <si>
+    <t>UK640R</t>
+  </si>
+  <si>
+    <t>SM PORTLAND</t>
+  </si>
+  <si>
+    <t>EVER SALUTE</t>
+  </si>
+  <si>
+    <t>494-129E</t>
+  </si>
+  <si>
+    <t>CMA CGM FORT JAMES</t>
+  </si>
+  <si>
+    <t>CPN040S19</t>
+  </si>
+  <si>
+    <t>PN3</t>
+  </si>
+  <si>
+    <t>YM WEALTH</t>
+  </si>
+  <si>
+    <t>PN32637W</t>
+  </si>
+  <si>
+    <t>MSC IVANA</t>
+  </si>
+  <si>
+    <t>UK638A</t>
+  </si>
+  <si>
+    <t>YM PLUM</t>
+  </si>
+  <si>
+    <t>PN12640E</t>
+  </si>
+  <si>
+    <t>YM TUTORIAL</t>
+  </si>
+  <si>
+    <t>LIBERTY PASSION</t>
   </si>
   <si>
     <t>Liberty</t>
   </si>
   <si>
-    <t>Inchcape</t>
-  </si>
-  <si>
     <t>Pacific Terminals</t>
   </si>
   <si>
-    <t>Seattle</t>
-  </si>
-  <si>
-    <t>T18</t>
+    <t>FRANKFURT EXPRESS</t>
+  </si>
+  <si>
+    <t>640E/643W</t>
+  </si>
+  <si>
+    <t>PATARA</t>
+  </si>
+  <si>
+    <t>005A</t>
+  </si>
+  <si>
+    <t>EVER MODE</t>
+  </si>
+  <si>
+    <t>1473-010E</t>
   </si>
   <si>
     <t>Oceania</t>
   </si>
   <si>
-    <t>LONG BEACH EXPRESS</t>
-  </si>
-  <si>
-    <t>636N/642S</t>
-  </si>
-  <si>
-    <t>Hapag-Lloyd</t>
-  </si>
-  <si>
-    <t>In transit</t>
-  </si>
-  <si>
-    <t>EB Service 2</t>
-  </si>
-  <si>
-    <t>SUVA CHIEF</t>
-  </si>
-  <si>
-    <t>007E/008W</t>
-  </si>
-  <si>
-    <t>Swire</t>
-  </si>
-  <si>
-    <t>Talon Marine Services LLC</t>
-  </si>
-  <si>
-    <t>CMA CGM BYBLOS</t>
-  </si>
-  <si>
-    <t>CPN00/CPN01</t>
-  </si>
-  <si>
-    <t>CMA CGM</t>
-  </si>
-  <si>
-    <t>T5</t>
-  </si>
-  <si>
-    <t>CLX</t>
-  </si>
-  <si>
-    <t>CAPE TAINARO</t>
-  </si>
-  <si>
-    <t>MC642R</t>
-  </si>
-  <si>
-    <t>MSC</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>Matson - AK</t>
-  </si>
-  <si>
-    <t>MATSON KODIAK</t>
-  </si>
-  <si>
-    <t>641S</t>
-  </si>
-  <si>
-    <t>Matson</t>
-  </si>
-  <si>
-    <t>SSA Marine</t>
-  </si>
-  <si>
-    <t>Waiting 2.9 days</t>
-  </si>
-  <si>
-    <t>Matson - HI2</t>
-  </si>
-  <si>
-    <t>MANULANI</t>
-  </si>
-  <si>
-    <t>IRIS ACE</t>
-  </si>
-  <si>
-    <t>110A</t>
-  </si>
-  <si>
-    <t>ONE</t>
-  </si>
-  <si>
-    <t>Ro-Ro</t>
-  </si>
-  <si>
-    <t>PNW1</t>
-  </si>
-  <si>
-    <t>OOCL NEW YORK</t>
-  </si>
-  <si>
-    <t>122E/122W</t>
-  </si>
-  <si>
-    <t>OOCL</t>
-  </si>
-  <si>
-    <t>TOTE</t>
-  </si>
-  <si>
-    <t>Tote - AK2</t>
-  </si>
-  <si>
-    <t>NORTH STAR</t>
-  </si>
-  <si>
-    <t>Tote</t>
-  </si>
-  <si>
-    <t>Tote Maritime Alaska Inc</t>
-  </si>
-  <si>
-    <t>Multipurpose</t>
-  </si>
-  <si>
-    <t>Husky</t>
-  </si>
-  <si>
-    <t>WC4/TP5</t>
-  </si>
-  <si>
-    <t>MAERSK TORINO</t>
-  </si>
-  <si>
-    <t>639E/642W</t>
-  </si>
-  <si>
-    <t>Maersk</t>
-  </si>
-  <si>
-    <t>CPNW</t>
-  </si>
-  <si>
-    <t>CMA CGM ALMAVIVA</t>
-  </si>
-  <si>
-    <t>CPN02/CPN03</t>
-  </si>
-  <si>
-    <t>CPV</t>
-  </si>
-  <si>
-    <t>XIN YING KOU</t>
-  </si>
-  <si>
-    <t>269N/269S</t>
-  </si>
-  <si>
-    <t>COSCO</t>
-  </si>
-  <si>
-    <t>COSCO SHIPPING LINES</t>
-  </si>
-  <si>
-    <t>THEMISA</t>
-  </si>
-  <si>
-    <t>ED615</t>
-  </si>
-  <si>
-    <t>Wallenius</t>
-  </si>
-  <si>
-    <t>SALVIA ACE</t>
-  </si>
-  <si>
-    <t>177A</t>
-  </si>
-  <si>
-    <t>FP2</t>
-  </si>
-  <si>
-    <t>ONE OWL</t>
-  </si>
-  <si>
-    <t>SM QINGDAO</t>
-  </si>
-  <si>
-    <t>2607E/2607W</t>
-  </si>
-  <si>
-    <t>SM Line</t>
-  </si>
-  <si>
-    <t>PCT</t>
-  </si>
-  <si>
-    <t>TPN</t>
-  </si>
-  <si>
-    <t>EVER ELITE</t>
-  </si>
-  <si>
-    <t>186W</t>
-  </si>
-  <si>
-    <t>Evergreen</t>
-  </si>
-  <si>
-    <t>BEN LINES</t>
-  </si>
-  <si>
-    <t>PN1</t>
-  </si>
-  <si>
-    <t>YM COSMOS</t>
-  </si>
-  <si>
-    <t>PN12639W</t>
-  </si>
-  <si>
-    <t>Yang Ming</t>
-  </si>
-  <si>
-    <t>Chinook</t>
-  </si>
-  <si>
-    <t>MSC DENISSE X</t>
-  </si>
-  <si>
-    <t>UK641R</t>
-  </si>
-  <si>
-    <t>MODERN LINK</t>
-  </si>
-  <si>
-    <t>T7</t>
-  </si>
-  <si>
-    <t>THEMIS LEADER</t>
-  </si>
-  <si>
-    <t>MATSON ANCHORAGE</t>
-  </si>
-  <si>
-    <t>643S</t>
-  </si>
-  <si>
-    <t>VIENNA EXPRESS</t>
-  </si>
-  <si>
-    <t>638E/641W</t>
-  </si>
-  <si>
-    <t>Tote - AK1</t>
-  </si>
-  <si>
-    <t>MIDNIGHT SUN</t>
-  </si>
-  <si>
-    <t>EVER MACH</t>
-  </si>
-  <si>
-    <t>018W</t>
-  </si>
-  <si>
-    <t>BEN LINE</t>
-  </si>
-  <si>
-    <t>COSCO VENICE</t>
-  </si>
-  <si>
-    <t>081N/081S</t>
-  </si>
-  <si>
-    <t>MSC FLORA</t>
-  </si>
-  <si>
-    <t>MC636A</t>
-  </si>
-  <si>
-    <t>ARC ENDEAVOR</t>
-  </si>
-  <si>
-    <t>A6180</t>
-  </si>
-  <si>
-    <t>Ports America Group/Pct</t>
-  </si>
-  <si>
-    <t>EB Service 1</t>
-  </si>
-  <si>
-    <t>WESTWOOD RAINIER</t>
-  </si>
-  <si>
-    <t>159E</t>
-  </si>
-  <si>
-    <t>R.J. PFEIFFER</t>
-  </si>
-  <si>
-    <t>KW664</t>
-  </si>
-  <si>
-    <t>CARNATION ACE</t>
-  </si>
-  <si>
-    <t>107A</t>
-  </si>
-  <si>
-    <t>OOCL SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>199E/199W</t>
-  </si>
-  <si>
-    <t>MAUNAWILI</t>
-  </si>
-  <si>
-    <t>642S</t>
-  </si>
-  <si>
-    <t>RJ PFEIFFER</t>
-  </si>
-  <si>
-    <t>POLARIS MILA</t>
-  </si>
-  <si>
-    <t>ARC HONOR</t>
-  </si>
-  <si>
-    <t>ED616</t>
-  </si>
-  <si>
-    <t>ARC INDEPENDENCE</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>EXPRESS ROME</t>
-  </si>
-  <si>
-    <t>UK640R</t>
-  </si>
-  <si>
-    <t>SM PORTLAND</t>
-  </si>
-  <si>
-    <t>EVER SALUTE</t>
-  </si>
-  <si>
-    <t>494-129E</t>
-  </si>
-  <si>
-    <t>CMA CGM FORT JAMES</t>
-  </si>
-  <si>
-    <t>CPN040S19</t>
-  </si>
-  <si>
-    <t>PN3</t>
-  </si>
-  <si>
-    <t>YM WEALTH</t>
-  </si>
-  <si>
-    <t>PN32637W</t>
-  </si>
-  <si>
-    <t>MSC IVANA</t>
-  </si>
-  <si>
-    <t>UK638A</t>
-  </si>
-  <si>
-    <t>YM PLUM</t>
-  </si>
-  <si>
-    <t>PN12640E</t>
-  </si>
-  <si>
-    <t>YM TUTORIAL</t>
-  </si>
-  <si>
-    <t>LIBERTY PASSION</t>
-  </si>
-  <si>
-    <t>FRANKFURT EXPRESS</t>
-  </si>
-  <si>
-    <t>640E/643W</t>
-  </si>
-  <si>
-    <t>PATARA</t>
-  </si>
-  <si>
-    <t>005A</t>
+    <t>CMA CGM DUTCH HARBOR</t>
+  </si>
+  <si>
+    <t>638N</t>
+  </si>
+  <si>
+    <t>MSC NITYA B</t>
+  </si>
+  <si>
+    <t>MC637A</t>
+  </si>
+  <si>
+    <t>NADI CHIEF</t>
+  </si>
+  <si>
+    <t>14E</t>
+  </si>
+  <si>
+    <t>ONE SYNERGY</t>
+  </si>
+  <si>
+    <t>FP22632C</t>
   </si>
   <si>
     <t>ONE DURBAN</t>
@@ -542,36 +551,6 @@
     <t>NBBT0001E</t>
   </si>
   <si>
-    <t>EVER MODE</t>
-  </si>
-  <si>
-    <t>1473-010E</t>
-  </si>
-  <si>
-    <t>CMA CGM DUTCH HARBOR</t>
-  </si>
-  <si>
-    <t>638N</t>
-  </si>
-  <si>
-    <t>MSC NITYA B</t>
-  </si>
-  <si>
-    <t>MC637A</t>
-  </si>
-  <si>
-    <t>NADI CHIEF</t>
-  </si>
-  <si>
-    <t>14E</t>
-  </si>
-  <si>
-    <t>ONE SYNERGY</t>
-  </si>
-  <si>
-    <t>FP22632C</t>
-  </si>
-  <si>
     <t>MSC SOLA</t>
   </si>
   <si>
@@ -653,19 +632,19 @@
     <t>UK640A</t>
   </si>
   <si>
+    <t>TONGALA</t>
+  </si>
+  <si>
+    <t>KW666</t>
+  </si>
+  <si>
+    <t>Jones Stevedoring Co</t>
+  </si>
+  <si>
+    <t>GLOVIS TREASURE</t>
+  </si>
+  <si>
     <t>GLOVIS LEGEND</t>
-  </si>
-  <si>
-    <t>GLOVIS TREASURE</t>
-  </si>
-  <si>
-    <t>TONGALA</t>
-  </si>
-  <si>
-    <t>KW666</t>
-  </si>
-  <si>
-    <t>Jones Stevedoring Co</t>
   </si>
   <si>
     <t>MSC SABRINA</t>
@@ -759,10 +738,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L105" totalsRowShown="0">
-  <autoFilter ref="A1:L105" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L105">
-    <sortCondition ref="J2:J105"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L100" totalsRowShown="0">
+  <autoFilter ref="A1:L100" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L100">
+    <sortCondition ref="J2:J100"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1099,7 +1078,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L105"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1164,23 +1143,26 @@
       <c r="D2" t="s">
         <v>15</v>
       </c>
+      <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" s="2">
-        <v>46309.208333333336</v>
+        <v>46310.25</v>
       </c>
       <c r="K2" s="2">
-        <v>46310.75</v>
+        <v>46311.708333333336</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1188,34 +1170,34 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J3" s="2">
-        <v>46309.75</v>
+        <v>46310.583333333336</v>
       </c>
       <c r="K3" s="2">
-        <v>46310.666666666664</v>
+        <v>46312.166666666664</v>
       </c>
       <c r="L3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1223,215 +1205,221 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" t="s">
         <v>25</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="1">
-        <v>4</v>
-      </c>
-      <c r="F4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
       <c r="I4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J4" s="2">
-        <v>46310.25</v>
+        <v>46310.708333333336</v>
       </c>
       <c r="K4" s="2">
-        <v>46310.75</v>
+        <v>46312.291666666664</v>
       </c>
       <c r="L4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>37</v>
+      </c>
+      <c r="H5" t="s">
+        <v>38</v>
       </c>
       <c r="I5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" s="2">
-        <v>46310.25</v>
+        <v>46311.104166666664</v>
       </c>
       <c r="K5" s="2">
-        <v>46310.75</v>
+        <v>46311.916666666664</v>
       </c>
       <c r="L5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" t="s">
         <v>37</v>
       </c>
-      <c r="D6" t="s">
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" t="s">
-        <v>41</v>
-      </c>
       <c r="I6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" s="2">
-        <v>46310.25</v>
+        <v>46311.333333333336</v>
       </c>
       <c r="K6" s="2">
-        <v>46311.708333333336</v>
+        <v>46312.125</v>
       </c>
       <c r="L6" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7" t="s">
-        <v>17</v>
+        <v>25</v>
+      </c>
+      <c r="H7" t="s">
+        <v>38</v>
       </c>
       <c r="I7" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="J7" s="2">
-        <v>46310.583333333336</v>
+        <v>46311.541666666664</v>
       </c>
       <c r="K7" s="2">
-        <v>46312.166666666664</v>
+        <v>46312.083333333336</v>
       </c>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G8" t="s">
-        <v>17</v>
+        <v>51</v>
+      </c>
+      <c r="H8" t="s">
+        <v>38</v>
       </c>
       <c r="I8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J8" s="2">
-        <v>46310.708333333336</v>
+        <v>46311.625</v>
       </c>
       <c r="K8" s="2">
-        <v>46312.291666666664</v>
+        <v>46312.708333333336</v>
       </c>
       <c r="L8" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="E9" s="1">
+        <v>26164</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I9" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="J9" s="2">
-        <v>46311.104166666664</v>
+        <v>46311.625</v>
       </c>
       <c r="K9" s="2">
-        <v>46311.916666666664</v>
+        <v>46312.041666666664</v>
       </c>
       <c r="L9" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1439,110 +1427,110 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" t="s">
         <v>50</v>
       </c>
-      <c r="C10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
       <c r="G10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H10" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J10" s="2">
-        <v>46311.333333333336</v>
+        <v>46311.625</v>
       </c>
       <c r="K10" s="2">
-        <v>46312.125</v>
+        <v>46312.708333333336</v>
       </c>
       <c r="L10" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="G11" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H11" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="I11" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="J11" s="2">
-        <v>46311.541666666664</v>
+        <v>46312.125</v>
       </c>
       <c r="K11" s="2">
-        <v>46312.083333333336</v>
+        <v>46312.666666666664</v>
       </c>
       <c r="L11" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" t="s">
         <v>63</v>
       </c>
-      <c r="D12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" t="s">
-        <v>66</v>
-      </c>
       <c r="G12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H12" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J12" s="2">
-        <v>46311.625</v>
+        <v>46312.3125</v>
       </c>
       <c r="K12" s="2">
-        <v>46312.708333333336</v>
+        <v>46314.75</v>
       </c>
       <c r="L12" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1550,156 +1538,147 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="1">
-        <v>26164</v>
+        <v>65</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="F13" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="G13" t="s">
-        <v>71</v>
-      </c>
-      <c r="H13" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="I13" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="J13" s="2">
-        <v>46311.625</v>
+        <v>46312.541666666664</v>
       </c>
       <c r="K13" s="2">
-        <v>46312.041666666664</v>
+        <v>46314.791666666664</v>
       </c>
       <c r="L13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H14" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="I14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" s="2">
-        <v>46311.625</v>
+        <v>46312.75</v>
       </c>
       <c r="K14" s="2">
-        <v>46312.708333333336</v>
+        <v>46313.75</v>
       </c>
       <c r="L14" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15" t="s">
         <v>25</v>
       </c>
-      <c r="C15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G15" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" t="s">
-        <v>55</v>
-      </c>
       <c r="I15" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="J15" s="2">
-        <v>46312.125</v>
+        <v>46314.25</v>
       </c>
       <c r="K15" s="2">
-        <v>46312.666666666664</v>
+        <v>46314.75</v>
       </c>
       <c r="L15" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F16" t="s">
-        <v>77</v>
-      </c>
-      <c r="G16" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" t="s">
-        <v>18</v>
-      </c>
       <c r="J16" s="2">
-        <v>46312.3125</v>
+        <v>46314.25</v>
       </c>
       <c r="K16" s="2">
         <v>46314.75</v>
       </c>
       <c r="L16" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
         <v>78</v>
@@ -1707,131 +1686,131 @@
       <c r="D17" t="s">
         <v>79</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>80</v>
+      <c r="E17" s="1">
+        <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G17" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J17" s="2">
-        <v>46312.541666666664</v>
+        <v>46314.625</v>
       </c>
       <c r="K17" s="2">
-        <v>46314.791666666664</v>
+        <v>46318.75</v>
       </c>
       <c r="L17" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D18" t="s">
+      <c r="F18" t="s">
         <v>82</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F18" t="s">
-        <v>84</v>
-      </c>
       <c r="G18" t="s">
-        <v>85</v>
+        <v>25</v>
+      </c>
+      <c r="H18" t="s">
+        <v>38</v>
       </c>
       <c r="I18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" s="2">
-        <v>46312.75</v>
+        <v>46314.625</v>
       </c>
       <c r="K18" s="2">
-        <v>46313.75</v>
+        <v>46315.166666666664</v>
       </c>
       <c r="L18" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
+        <v>85</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" t="s">
         <v>87</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>88</v>
       </c>
-      <c r="G19" t="s">
-        <v>17</v>
-      </c>
       <c r="I19" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J19" s="2">
-        <v>46314.25</v>
+        <v>46315.208333333336</v>
       </c>
       <c r="K19" s="2">
-        <v>46314.75</v>
+        <v>46316.791666666664</v>
       </c>
       <c r="L19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F20" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="G20" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="I20" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J20" s="2">
-        <v>46314.25</v>
+        <v>46315.25</v>
       </c>
       <c r="K20" s="2">
-        <v>46314.75</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1839,282 +1818,282 @@
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
-      </c>
-      <c r="E21" s="1">
-        <v>34</v>
+        <v>95</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="F21" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="G21" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J21" s="2">
-        <v>46314.625</v>
+        <v>46315.291666666664</v>
       </c>
       <c r="K21" s="2">
-        <v>46318.75</v>
+        <v>46317.75</v>
       </c>
       <c r="L21" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>58</v>
+      </c>
+      <c r="C22" t="s">
+        <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>93</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G22" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="I22" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="J22" s="2">
-        <v>46314.625</v>
+        <v>46315.541666666664</v>
       </c>
       <c r="K22" s="2">
-        <v>46315.166666666664</v>
+        <v>46316.75</v>
       </c>
       <c r="L22" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="D23" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="E23" s="1">
+        <v>63</v>
       </c>
       <c r="F23" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="G23" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="I23" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="J23" s="2">
-        <v>46315.208333333336</v>
+        <v>46316.25</v>
       </c>
       <c r="K23" s="2">
-        <v>46316.791666666664</v>
+        <v>46316.75</v>
       </c>
       <c r="L23" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" t="s">
+        <v>101</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D24" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="F24" t="s">
-        <v>105</v>
+        <v>37</v>
       </c>
       <c r="G24" t="s">
-        <v>28</v>
+        <v>37</v>
+      </c>
+      <c r="H24" t="s">
+        <v>38</v>
       </c>
       <c r="I24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J24" s="2">
-        <v>46315.25</v>
+        <v>46316.291666666664</v>
       </c>
       <c r="K24" s="2">
-        <v>46317.166666666664</v>
+        <v>46316.916666666664</v>
       </c>
       <c r="L24" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F25" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="G25" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J25" s="2">
-        <v>46315.291666666664</v>
+        <v>46316.625</v>
       </c>
       <c r="K25" s="2">
-        <v>46317.75</v>
+        <v>46319.75</v>
       </c>
       <c r="L25" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" t="s">
+        <v>103</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" t="s">
+        <v>105</v>
+      </c>
+      <c r="G26" t="s">
         <v>25</v>
       </c>
-      <c r="C26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" t="s">
-        <v>109</v>
-      </c>
-      <c r="E26" s="1">
-        <v>2</v>
-      </c>
-      <c r="F26" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" t="s">
-        <v>17</v>
-      </c>
       <c r="I26" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J26" s="2">
-        <v>46315.541666666664</v>
+        <v>46316.625</v>
       </c>
       <c r="K26" s="2">
-        <v>46316.75</v>
+        <v>46319.75</v>
       </c>
       <c r="L26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="C27" t="s">
-        <v>14</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E27" s="1">
-        <v>63</v>
+        <v>26169</v>
       </c>
       <c r="F27" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G27" t="s">
-        <v>28</v>
+        <v>56</v>
+      </c>
+      <c r="H27" t="s">
+        <v>56</v>
       </c>
       <c r="I27" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="J27" s="2">
-        <v>46316.25</v>
+        <v>46316.625</v>
       </c>
       <c r="K27" s="2">
-        <v>46316.75</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L27" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F28" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="G28" t="s">
-        <v>54</v>
-      </c>
-      <c r="H28" t="s">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="I28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J28" s="2">
-        <v>46316.291666666664</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K28" s="2">
-        <v>46316.916666666664</v>
+        <v>46318.708333333336</v>
       </c>
       <c r="L28" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2122,34 +2101,34 @@
         <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F29" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="G29" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="I29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J29" s="2">
-        <v>46316.625</v>
+        <v>46317.25</v>
       </c>
       <c r="K29" s="2">
-        <v>46319.75</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L29" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2157,72 +2136,69 @@
         <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="D30" t="s">
-        <v>117</v>
-      </c>
-      <c r="E30" s="1">
-        <v>26169</v>
+        <v>113</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="F30" t="s">
-        <v>70</v>
-      </c>
-      <c r="G30" t="s">
-        <v>71</v>
-      </c>
-      <c r="H30" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="I30" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="J30" s="2">
-        <v>46316.625</v>
+        <v>46317.291666666664</v>
       </c>
       <c r="K30" s="2">
-        <v>46317.041666666664</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C31" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" t="s">
+        <v>115</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F31" t="s">
         <v>74</v>
       </c>
-      <c r="D31" t="s">
-        <v>114</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F31" t="s">
-        <v>35</v>
-      </c>
       <c r="G31" t="s">
-        <v>17</v>
+        <v>25</v>
+      </c>
+      <c r="H31" t="s">
+        <v>117</v>
       </c>
       <c r="I31" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="J31" s="2">
-        <v>46316.625</v>
+        <v>46317.666666666664</v>
       </c>
       <c r="K31" s="2">
-        <v>46319.75</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L31" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -2230,390 +2206,390 @@
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>13</v>
+      </c>
+      <c r="C32" t="s">
+        <v>118</v>
       </c>
       <c r="D32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F32" t="s">
-        <v>100</v>
-      </c>
-      <c r="G32" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="I32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J32" s="2">
-        <v>46317.208333333336</v>
+        <v>46317.927777777775</v>
       </c>
       <c r="K32" s="2">
-        <v>46318.708333333336</v>
+        <v>46318.969444444447</v>
       </c>
       <c r="L32" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="D33" t="s">
         <v>121</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="F33" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="G33" t="s">
-        <v>85</v>
+        <v>37</v>
+      </c>
+      <c r="H33" t="s">
+        <v>38</v>
       </c>
       <c r="I33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J33" s="2">
-        <v>46317.25</v>
+        <v>46318.104166666664</v>
       </c>
       <c r="K33" s="2">
-        <v>46318.166666666664</v>
+        <v>46318.916666666664</v>
       </c>
       <c r="L33" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C34" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D34" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F34" t="s">
-        <v>49</v>
+        <v>74</v>
+      </c>
+      <c r="G34" t="s">
+        <v>25</v>
+      </c>
+      <c r="H34" t="s">
+        <v>117</v>
       </c>
       <c r="I34" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="J34" s="2">
-        <v>46317.291666666664</v>
+        <v>46318.208333333336</v>
       </c>
       <c r="K34" s="2">
-        <v>46318.166666666664</v>
+        <v>46319.125</v>
       </c>
       <c r="L34" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B35" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" t="s">
+        <v>123</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F35" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35" t="s">
         <v>25</v>
       </c>
-      <c r="C35" t="s">
-        <v>14</v>
-      </c>
-      <c r="D35" t="s">
-        <v>125</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F35" t="s">
-        <v>88</v>
-      </c>
-      <c r="G35" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" t="s">
-        <v>127</v>
-      </c>
       <c r="I35" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="J35" s="2">
-        <v>46317.666666666664</v>
+        <v>46318.25</v>
       </c>
       <c r="K35" s="2">
-        <v>46318.166666666664</v>
+        <v>46318.75</v>
       </c>
       <c r="L35" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>128</v>
+        <v>47</v>
       </c>
       <c r="D36" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F36" t="s">
-        <v>40</v>
+        <v>50</v>
+      </c>
+      <c r="G36" t="s">
+        <v>51</v>
+      </c>
+      <c r="H36" t="s">
+        <v>38</v>
       </c>
       <c r="I36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J36" s="2">
-        <v>46317.927777777775</v>
+        <v>46318.25</v>
       </c>
       <c r="K36" s="2">
-        <v>46318.969444444447</v>
+        <v>46319.166666666664</v>
       </c>
       <c r="L36" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>131</v>
+        <v>127</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="F37" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="G37" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="H37" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="I37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J37" s="2">
-        <v>46318.104166666664</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K37" s="2">
-        <v>46318.916666666664</v>
+        <v>46319.125</v>
       </c>
       <c r="L37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="D38" t="s">
-        <v>125</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>132</v>
+        <v>54</v>
+      </c>
+      <c r="E38" s="1">
+        <v>26168</v>
       </c>
       <c r="F38" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="G38" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="H38" t="s">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="I38" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="J38" s="2">
-        <v>46318.208333333336</v>
+        <v>46318.625</v>
       </c>
       <c r="K38" s="2">
-        <v>46319.125</v>
+        <v>46319.041666666664</v>
       </c>
       <c r="L38" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D39" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F39" t="s">
-        <v>61</v>
-      </c>
-      <c r="G39" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="I39" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J39" s="2">
-        <v>46318.25</v>
+        <v>46318.704861111109</v>
       </c>
       <c r="K39" s="2">
-        <v>46318.75</v>
+        <v>46319.204861111109</v>
       </c>
       <c r="L39" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="C40" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="D40" t="s">
-        <v>135</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
+      </c>
+      <c r="E40" s="1">
+        <v>4</v>
       </c>
       <c r="F40" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="G40" t="s">
-        <v>28</v>
-      </c>
-      <c r="H40" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="I40" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="J40" s="2">
-        <v>46318.25</v>
+        <v>46319.208333333336</v>
       </c>
       <c r="K40" s="2">
-        <v>46319.166666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L40" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C41" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="D41" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="F41" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="G41" t="s">
-        <v>54</v>
-      </c>
-      <c r="H41" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="I41" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="J41" s="2">
-        <v>46318.291666666664</v>
+        <v>46319.25</v>
       </c>
       <c r="K41" s="2">
-        <v>46319.125</v>
+        <v>46319.75</v>
       </c>
       <c r="L41" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B42" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="C42" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>69</v>
+        <v>133</v>
       </c>
       <c r="E42" s="1">
-        <v>26168</v>
+        <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>70</v>
+        <v>134</v>
       </c>
       <c r="G42" t="s">
-        <v>71</v>
-      </c>
-      <c r="H42" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="I42" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J42" s="2">
-        <v>46318.625</v>
+        <v>46319.25</v>
       </c>
       <c r="K42" s="2">
-        <v>46319.041666666664</v>
+        <v>46322.75</v>
       </c>
       <c r="L42" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2621,31 +2597,34 @@
         <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="D43" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F43" t="s">
-        <v>54</v>
+        <v>31</v>
+      </c>
+      <c r="G43" t="s">
+        <v>25</v>
       </c>
       <c r="I43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J43" s="2">
-        <v>46318.704861111109</v>
+        <v>46319.291666666664</v>
       </c>
       <c r="K43" s="2">
-        <v>46319.204861111109</v>
+        <v>46320.75</v>
       </c>
       <c r="L43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2653,69 +2632,66 @@
         <v>12</v>
       </c>
       <c r="B44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" t="s">
+        <v>137</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F44" t="s">
+        <v>82</v>
+      </c>
+      <c r="G44" t="s">
         <v>25</v>
       </c>
-      <c r="C44" t="s">
-        <v>14</v>
-      </c>
-      <c r="D44" t="s">
-        <v>140</v>
-      </c>
-      <c r="E44" s="1">
-        <v>4</v>
-      </c>
-      <c r="F44" t="s">
-        <v>23</v>
-      </c>
-      <c r="G44" t="s">
-        <v>17</v>
+      <c r="H44" t="s">
+        <v>38</v>
       </c>
       <c r="I44" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J44" s="2">
-        <v>46319.208333333336</v>
+        <v>46319.625</v>
       </c>
       <c r="K44" s="2">
-        <v>46319.75</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="D45" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F45" t="s">
-        <v>88</v>
-      </c>
-      <c r="G45" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="I45" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J45" s="2">
-        <v>46319.25</v>
+        <v>46320</v>
       </c>
       <c r="K45" s="2">
-        <v>46319.75</v>
+        <v>46322</v>
       </c>
       <c r="L45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2723,410 +2699,404 @@
         <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="D46" t="s">
-        <v>143</v>
-      </c>
-      <c r="E46" s="1">
-        <v>1</v>
+        <v>140</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="F46" t="s">
-        <v>144</v>
-      </c>
-      <c r="G46" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I46" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J46" s="2">
-        <v>46319.25</v>
+        <v>46320.21875</v>
       </c>
       <c r="K46" s="2">
-        <v>46322.75</v>
+        <v>46324.59375</v>
       </c>
       <c r="L46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B47" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="C47" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="D47" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F47" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="G47" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="I47" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J47" s="2">
-        <v>46319.291666666664</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K47" s="2">
-        <v>46320.75</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L47" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C48" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" t="s">
+        <v>145</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F48" t="s">
         <v>31</v>
       </c>
-      <c r="D48" t="s">
-        <v>147</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F48" t="s">
-        <v>95</v>
-      </c>
-      <c r="G48" t="s">
-        <v>17</v>
-      </c>
-      <c r="H48" t="s">
-        <v>55</v>
-      </c>
       <c r="I48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J48" s="2">
-        <v>46319.625</v>
+        <v>46321.21875</v>
       </c>
       <c r="K48" s="2">
-        <v>46320.166666666664</v>
+        <v>46323.21875</v>
       </c>
       <c r="L48" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C49" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D49" t="s">
+        <v>147</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="F49" t="s">
-        <v>100</v>
+        <v>93</v>
+      </c>
+      <c r="G49" t="s">
+        <v>51</v>
       </c>
       <c r="I49" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J49" s="2">
-        <v>46320</v>
+        <v>46321.25</v>
       </c>
       <c r="K49" s="2">
-        <v>46322</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L49" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="C50" t="s">
         <v>78</v>
       </c>
       <c r="D50" t="s">
-        <v>150</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
+      </c>
+      <c r="E50" s="1">
+        <v>21</v>
       </c>
       <c r="F50" t="s">
-        <v>44</v>
+        <v>93</v>
+      </c>
+      <c r="G50" t="s">
+        <v>25</v>
       </c>
       <c r="I50" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J50" s="2">
-        <v>46320.21875</v>
+        <v>46321.625</v>
       </c>
       <c r="K50" s="2">
-        <v>46324.59375</v>
+        <v>46325.75</v>
       </c>
       <c r="L50" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" t="s">
+        <v>150</v>
+      </c>
+      <c r="F51" t="s">
+        <v>151</v>
+      </c>
+      <c r="G51" t="s">
+        <v>51</v>
+      </c>
+      <c r="H51" t="s">
         <v>152</v>
       </c>
-      <c r="D51" t="s">
-        <v>153</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F51" t="s">
-        <v>105</v>
-      </c>
-      <c r="G51" t="s">
-        <v>28</v>
-      </c>
       <c r="I51" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="J51" s="2">
-        <v>46321.208333333336</v>
+        <v>46322.25</v>
       </c>
       <c r="K51" s="2">
-        <v>46323.166666666664</v>
+        <v>46322.75</v>
       </c>
       <c r="L51" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B52" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C52" t="s">
-        <v>106</v>
+        <v>60</v>
       </c>
       <c r="D52" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F52" t="s">
-        <v>49</v>
+        <v>105</v>
+      </c>
+      <c r="G52" t="s">
+        <v>25</v>
       </c>
       <c r="I52" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J52" s="2">
-        <v>46321.21875</v>
+        <v>46322.625</v>
       </c>
       <c r="K52" s="2">
-        <v>46323.21875</v>
+        <v>46325.75</v>
       </c>
       <c r="L52" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B53" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="D53" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F53" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="G53" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I53" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="J53" s="2">
-        <v>46321.25</v>
+        <v>46323.25</v>
       </c>
       <c r="K53" s="2">
-        <v>46323.166666666664</v>
+        <v>46323.75</v>
       </c>
       <c r="L53" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B54" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="C54" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="D54" t="s">
-        <v>159</v>
-      </c>
-      <c r="E54" s="1">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F54" t="s">
-        <v>105</v>
-      </c>
-      <c r="G54" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="I54" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J54" s="2">
-        <v>46321.625</v>
+        <v>46323.291666666664</v>
       </c>
       <c r="K54" s="2">
-        <v>46325.75</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="L54" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B55" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="C55" t="s">
-        <v>14</v>
+        <v>106</v>
       </c>
       <c r="D55" t="s">
-        <v>160</v>
+        <v>107</v>
+      </c>
+      <c r="E55" s="1">
+        <v>26173</v>
       </c>
       <c r="F55" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="G55" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="H55" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="I55" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="J55" s="2">
-        <v>46322.25</v>
+        <v>46323.625</v>
       </c>
       <c r="K55" s="2">
-        <v>46322.75</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L55" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B56" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="C56" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F56" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G56" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I56" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="J56" s="2">
-        <v>46322.625</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K56" s="2">
-        <v>46325.75</v>
+        <v>46324.75</v>
       </c>
       <c r="L56" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B57" t="s">
-        <v>25</v>
-      </c>
-      <c r="C57" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="D57" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F57" t="s">
-        <v>61</v>
-      </c>
-      <c r="G57" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="I57" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J57" s="2">
-        <v>46323.25</v>
+        <v>46324</v>
       </c>
       <c r="K57" s="2">
-        <v>46323.75</v>
+        <v>46326</v>
       </c>
       <c r="L57" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3134,28 +3104,31 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>51</v>
+        <v>159</v>
       </c>
       <c r="D58" t="s">
-        <v>52</v>
+        <v>160</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="F58" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="I58" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J58" s="2">
-        <v>46323.291666666664</v>
+        <v>46324.647916666669</v>
       </c>
       <c r="K58" s="2">
-        <v>46323.791666666664</v>
+        <v>46326.147916666669</v>
       </c>
       <c r="L58" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3163,37 +3136,31 @@
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C59" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="D59" t="s">
-        <v>117</v>
-      </c>
-      <c r="E59" s="1">
-        <v>26173</v>
+        <v>162</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="F59" t="s">
-        <v>70</v>
-      </c>
-      <c r="G59" t="s">
-        <v>71</v>
-      </c>
-      <c r="H59" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="I59" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="J59" s="2">
-        <v>46323.625</v>
+        <v>46325.003472222219</v>
       </c>
       <c r="K59" s="2">
-        <v>46324.041666666664</v>
+        <v>46325.878472222219</v>
       </c>
       <c r="L59" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3204,383 +3171,389 @@
         <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>152</v>
+        <v>14</v>
       </c>
       <c r="D60" t="s">
+        <v>164</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="F60" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="I60" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J60" s="2">
-        <v>46323.661111111112</v>
+        <v>46325.056944444441</v>
       </c>
       <c r="K60" s="2">
-        <v>46327.202777777777</v>
+        <v>46326.098611111112</v>
       </c>
       <c r="L60" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C61" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="D61" t="s">
-        <v>165</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>166</v>
+        <v>101</v>
       </c>
       <c r="F61" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="I61" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J61" s="2">
-        <v>46323.661111111112</v>
+        <v>46325.333333333336</v>
       </c>
       <c r="K61" s="2">
-        <v>46327.202777777777</v>
+        <v>46325.833333333336</v>
       </c>
       <c r="L61" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B62" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="C62" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="D62" t="s">
-        <v>163</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>164</v>
+        <v>54</v>
+      </c>
+      <c r="E62" s="1">
+        <v>26172</v>
       </c>
       <c r="F62" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G62" t="s">
-        <v>17</v>
+        <v>56</v>
+      </c>
+      <c r="H62" t="s">
+        <v>56</v>
       </c>
       <c r="I62" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="J62" s="2">
-        <v>46323.791666666664</v>
+        <v>46325.625</v>
       </c>
       <c r="K62" s="2">
-        <v>46324.75</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L62" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B63" t="s">
-        <v>96</v>
+        <v>59</v>
+      </c>
+      <c r="C63" t="s">
+        <v>78</v>
       </c>
       <c r="D63" t="s">
+        <v>166</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E63" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="F63" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="I63" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J63" s="2">
-        <v>46324</v>
+        <v>46325.625</v>
       </c>
       <c r="K63" s="2">
-        <v>46326</v>
+        <v>46329.708333333336</v>
       </c>
       <c r="L63" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="C64" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="D64" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F64" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I64" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J64" s="2">
-        <v>46324.647916666669</v>
+        <v>46325.625</v>
       </c>
       <c r="K64" s="2">
-        <v>46326.147916666669</v>
+        <v>46329.708333333336</v>
       </c>
       <c r="L64" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B65" t="s">
+        <v>89</v>
+      </c>
+      <c r="C65" t="s">
+        <v>142</v>
+      </c>
+      <c r="D65" t="s">
+        <v>168</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F65" t="s">
         <v>45</v>
       </c>
-      <c r="C65" t="s">
-        <v>46</v>
-      </c>
-      <c r="D65" t="s">
-        <v>171</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="F65" t="s">
-        <v>49</v>
-      </c>
       <c r="I65" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J65" s="2">
-        <v>46325.003472222219</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K65" s="2">
-        <v>46325.878472222219</v>
+        <v>46328.916666666664</v>
       </c>
       <c r="L65" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B66" t="s">
+        <v>27</v>
+      </c>
+      <c r="C66" t="s">
+        <v>94</v>
+      </c>
+      <c r="D66" t="s">
+        <v>170</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F66" t="s">
         <v>31</v>
       </c>
-      <c r="C66" t="s">
-        <v>37</v>
-      </c>
-      <c r="D66" t="s">
-        <v>173</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="F66" t="s">
-        <v>40</v>
-      </c>
       <c r="I66" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J66" s="2">
-        <v>46325.056944444441</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K66" s="2">
-        <v>46326.098611111112</v>
+        <v>46328.125</v>
       </c>
       <c r="L66" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B67" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C67" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="D67" t="s">
-        <v>112</v>
+        <v>172</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="F67" t="s">
-        <v>54</v>
+        <v>45</v>
+      </c>
+      <c r="G67" t="s">
+        <v>25</v>
       </c>
       <c r="I67" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="J67" s="2">
-        <v>46325.333333333336</v>
+        <v>46326.25</v>
       </c>
       <c r="K67" s="2">
-        <v>46325.833333333336</v>
+        <v>46326.75</v>
       </c>
       <c r="L67" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B68" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C68" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D68" t="s">
-        <v>69</v>
-      </c>
-      <c r="E68" s="1">
-        <v>26172</v>
+        <v>174</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="F68" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G68" t="s">
-        <v>71</v>
-      </c>
-      <c r="H68" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="I68" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J68" s="2">
-        <v>46325.625</v>
+        <v>46326.25</v>
       </c>
       <c r="K68" s="2">
-        <v>46326.041666666664</v>
+        <v>46326.75</v>
       </c>
       <c r="L68" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B69" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="C69" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="D69" t="s">
-        <v>175</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>176</v>
+        <v>41</v>
       </c>
       <c r="F69" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="I69" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J69" s="2">
-        <v>46325.625</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K69" s="2">
-        <v>46329.708333333336</v>
+        <v>46326.75</v>
       </c>
       <c r="L69" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B70" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="C70" t="s">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="D70" t="s">
+        <v>174</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E70" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="F70" t="s">
-        <v>61</v>
+        <v>74</v>
+      </c>
+      <c r="G70" t="s">
+        <v>25</v>
       </c>
       <c r="I70" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="J70" s="2">
-        <v>46325.625</v>
+        <v>46326.791666666664</v>
       </c>
       <c r="K70" s="2">
-        <v>46329.708333333336</v>
+        <v>46327.75</v>
       </c>
       <c r="L70" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B71" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="C71" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="D71" t="s">
+        <v>176</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="F71" t="s">
         <v>178</v>
       </c>
-      <c r="F71" t="s">
-        <v>49</v>
-      </c>
       <c r="I71" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J71" s="2">
-        <v>46326.166666666664</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K71" s="2">
-        <v>46328.125</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L71" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3588,69 +3561,66 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="D72" t="s">
         <v>179</v>
       </c>
-      <c r="E72" s="1" t="s">
-        <v>180</v>
+      <c r="E72" s="1">
+        <v>69</v>
       </c>
       <c r="F72" t="s">
-        <v>61</v>
-      </c>
-      <c r="G72" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I72" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J72" s="2">
-        <v>46326.25</v>
+        <v>46327.166666666664</v>
       </c>
       <c r="K72" s="2">
-        <v>46326.75</v>
+        <v>46328.541666666664</v>
       </c>
       <c r="L72" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B73" t="s">
+        <v>42</v>
+      </c>
+      <c r="C73" t="s">
+        <v>21</v>
+      </c>
+      <c r="D73" t="s">
+        <v>180</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F73" t="s">
+        <v>45</v>
+      </c>
+      <c r="G73" t="s">
         <v>25</v>
       </c>
-      <c r="C73" t="s">
-        <v>14</v>
-      </c>
-      <c r="D73" t="s">
-        <v>181</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F73" t="s">
-        <v>88</v>
-      </c>
-      <c r="G73" t="s">
-        <v>17</v>
-      </c>
       <c r="I73" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="J73" s="2">
-        <v>46326.25</v>
+        <v>46327.25</v>
       </c>
       <c r="K73" s="2">
-        <v>46326.75</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="L73" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3658,386 +3628,377 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>50</v>
-      </c>
-      <c r="C74" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="D74" t="s">
-        <v>58</v>
+        <v>182</v>
       </c>
       <c r="F74" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="I74" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J74" s="2">
-        <v>46326.416666666664</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K74" s="2">
-        <v>46326.75</v>
+        <v>46328.833333333336</v>
       </c>
       <c r="L74" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B75" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="C75" t="s">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="D75" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F75" t="s">
-        <v>88</v>
-      </c>
-      <c r="G75" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="I75" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J75" s="2">
-        <v>46326.791666666664</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K75" s="2">
-        <v>46327.75</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L75" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B76" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="C76" t="s">
-        <v>152</v>
+        <v>84</v>
       </c>
       <c r="D76" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F76" t="s">
-        <v>185</v>
+        <v>87</v>
       </c>
       <c r="I76" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J76" s="2">
-        <v>46326.833333333336</v>
+        <v>46329</v>
       </c>
       <c r="K76" s="2">
-        <v>46329.583333333336</v>
+        <v>46330</v>
       </c>
       <c r="L76" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B77" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="C77" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="D77" t="s">
-        <v>186</v>
-      </c>
-      <c r="E77" s="1">
-        <v>69</v>
+        <v>187</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="F77" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="G77" t="s">
+        <v>25</v>
       </c>
       <c r="I77" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="J77" s="2">
-        <v>46327.166666666664</v>
+        <v>46329.25</v>
       </c>
       <c r="K77" s="2">
-        <v>46328.541666666664</v>
+        <v>46329.75</v>
       </c>
       <c r="L77" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B78" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="C78" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="D78" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F78" t="s">
-        <v>61</v>
-      </c>
-      <c r="G78" t="s">
-        <v>17</v>
+        <v>178</v>
       </c>
       <c r="I78" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J78" s="2">
-        <v>46327.25</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K78" s="2">
-        <v>46327.708333333336</v>
+        <v>46332.625</v>
       </c>
       <c r="L78" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B79" t="s">
-        <v>31</v>
+        <v>42</v>
+      </c>
+      <c r="C79" t="s">
+        <v>21</v>
       </c>
       <c r="D79" t="s">
-        <v>189</v>
+        <v>187</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="F79" t="s">
-        <v>95</v>
+        <v>45</v>
+      </c>
+      <c r="G79" t="s">
+        <v>25</v>
       </c>
       <c r="I79" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="J79" s="2">
-        <v>46327.708333333336</v>
+        <v>46329.791666666664</v>
       </c>
       <c r="K79" s="2">
-        <v>46328.833333333336</v>
+        <v>46330.75</v>
       </c>
       <c r="L79" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B80" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="C80" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="D80" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F80" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="I80" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J80" s="2">
-        <v>46327.904861111114</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K80" s="2">
-        <v>46331.196527777778</v>
+        <v>46334</v>
       </c>
       <c r="L80" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B81" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="C81" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D81" t="s">
+        <v>191</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="F81" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="I81" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J81" s="2">
-        <v>46329</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K81" s="2">
-        <v>46330</v>
+        <v>46334</v>
       </c>
       <c r="L81" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B82" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="C82" t="s">
-        <v>14</v>
+        <v>106</v>
       </c>
       <c r="D82" t="s">
-        <v>194</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>195</v>
+        <v>107</v>
       </c>
       <c r="F82" t="s">
-        <v>61</v>
-      </c>
-      <c r="G82" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="I82" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="J82" s="2">
-        <v>46329.25</v>
+        <v>46330.625</v>
       </c>
       <c r="K82" s="2">
-        <v>46329.75</v>
+        <v>46331.125</v>
       </c>
       <c r="L82" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B83" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="C83" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D83" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F83" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="I83" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J83" s="2">
-        <v>46329.333333333336</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K83" s="2">
-        <v>46332.625</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L83" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B84" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="C84" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="D84" t="s">
+        <v>193</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E84" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="F84" t="s">
-        <v>61</v>
-      </c>
-      <c r="G84" t="s">
-        <v>17</v>
+        <v>178</v>
       </c>
       <c r="I84" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J84" s="2">
-        <v>46329.791666666664</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K84" s="2">
-        <v>46330.75</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L84" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B85" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="C85" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="D85" t="s">
-        <v>198</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="F85" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="I85" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J85" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.704861111109</v>
       </c>
       <c r="K85" s="2">
-        <v>46334</v>
+        <v>46331.204861111109</v>
       </c>
       <c r="L85" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4045,124 +4006,139 @@
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="C86" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D86" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F86" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="I86" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J86" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.75</v>
       </c>
       <c r="K86" s="2">
-        <v>46334</v>
+        <v>46332.75</v>
       </c>
       <c r="L86" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B87" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C87" t="s">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="D87" t="s">
-        <v>117</v>
+        <v>197</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="F87" t="s">
-        <v>70</v>
+        <v>74</v>
+      </c>
+      <c r="G87" t="s">
+        <v>25</v>
+      </c>
+      <c r="H87" t="s">
+        <v>199</v>
       </c>
       <c r="I87" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J87" s="2">
-        <v>46330.625</v>
+        <v>46331.25</v>
       </c>
       <c r="K87" s="2">
-        <v>46331.125</v>
+        <v>46331.75</v>
       </c>
       <c r="L87" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B88" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C88" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="D88" t="s">
         <v>200</v>
       </c>
-      <c r="E88" s="1" t="s">
-        <v>201</v>
+      <c r="E88" s="1">
+        <v>10</v>
       </c>
       <c r="F88" t="s">
-        <v>185</v>
+        <v>98</v>
+      </c>
+      <c r="G88" t="s">
+        <v>25</v>
       </c>
       <c r="I88" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="J88" s="2">
-        <v>46330.633333333331</v>
+        <v>46331.25</v>
       </c>
       <c r="K88" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.75</v>
       </c>
       <c r="L88" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B89" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="C89" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="D89" t="s">
-        <v>200</v>
-      </c>
-      <c r="E89" s="1" t="s">
         <v>201</v>
       </c>
+      <c r="E89" s="1">
+        <v>1</v>
+      </c>
       <c r="F89" t="s">
-        <v>185</v>
+        <v>98</v>
+      </c>
+      <c r="G89" t="s">
+        <v>25</v>
       </c>
       <c r="I89" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="J89" s="2">
-        <v>46330.633333333331</v>
+        <v>46331.25</v>
       </c>
       <c r="K89" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.75</v>
       </c>
       <c r="L89" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4170,200 +4146,203 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C90" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="D90" t="s">
-        <v>139</v>
+        <v>202</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="F90" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="I90" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J90" s="2">
-        <v>46330.704861111109</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K90" s="2">
-        <v>46331.204861111109</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L90" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B91" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="C91" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="D91" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F91" t="s">
-        <v>49</v>
+        <v>178</v>
       </c>
       <c r="I91" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J91" s="2">
-        <v>46330.75</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K91" s="2">
-        <v>46332.75</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L91" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B92" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="C92" t="s">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="D92" t="s">
         <v>204</v>
       </c>
-      <c r="E92" s="1">
-        <v>1</v>
+      <c r="E92" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="F92" t="s">
-        <v>23</v>
-      </c>
-      <c r="G92" t="s">
-        <v>17</v>
+        <v>178</v>
       </c>
       <c r="I92" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J92" s="2">
-        <v>46331.25</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K92" s="2">
-        <v>46331.75</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L92" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B93" t="s">
+        <v>42</v>
+      </c>
+      <c r="C93" t="s">
+        <v>21</v>
+      </c>
+      <c r="D93" t="s">
+        <v>197</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F93" t="s">
+        <v>74</v>
+      </c>
+      <c r="G93" t="s">
         <v>25</v>
       </c>
-      <c r="C93" t="s">
-        <v>14</v>
-      </c>
-      <c r="D93" t="s">
-        <v>205</v>
-      </c>
-      <c r="E93" s="1">
-        <v>10</v>
-      </c>
-      <c r="F93" t="s">
-        <v>23</v>
-      </c>
-      <c r="G93" t="s">
-        <v>17</v>
+      <c r="H93" t="s">
+        <v>199</v>
       </c>
       <c r="I93" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="J93" s="2">
-        <v>46331.25</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K93" s="2">
-        <v>46331.75</v>
+        <v>46332.75</v>
       </c>
       <c r="L93" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B94" t="s">
+        <v>42</v>
+      </c>
+      <c r="C94" t="s">
+        <v>21</v>
+      </c>
+      <c r="D94" t="s">
+        <v>200</v>
+      </c>
+      <c r="E94" s="1">
+        <v>10</v>
+      </c>
+      <c r="F94" t="s">
+        <v>98</v>
+      </c>
+      <c r="G94" t="s">
         <v>25</v>
       </c>
-      <c r="C94" t="s">
-        <v>14</v>
-      </c>
-      <c r="D94" t="s">
-        <v>206</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F94" t="s">
-        <v>88</v>
-      </c>
-      <c r="G94" t="s">
-        <v>17</v>
-      </c>
-      <c r="H94" t="s">
-        <v>208</v>
-      </c>
       <c r="I94" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="J94" s="2">
-        <v>46331.25</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K94" s="2">
-        <v>46331.75</v>
+        <v>46332.75</v>
       </c>
       <c r="L94" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B95" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C95" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D95" t="s">
-        <v>209</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>210</v>
+        <v>201</v>
+      </c>
+      <c r="E95" s="1">
+        <v>1</v>
       </c>
       <c r="F95" t="s">
-        <v>49</v>
+        <v>98</v>
+      </c>
+      <c r="G95" t="s">
+        <v>25</v>
       </c>
       <c r="I95" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="J95" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K95" s="2">
-        <v>46332.166666666664</v>
+        <v>46332.75</v>
       </c>
       <c r="L95" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4374,60 +4353,57 @@
         <v>13</v>
       </c>
       <c r="C96" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D96" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F96" t="s">
-        <v>185</v>
+        <v>17</v>
       </c>
       <c r="I96" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J96" s="2">
-        <v>46331.496527777781</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K96" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L96" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B97" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C97" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="D97" t="s">
-        <v>211</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>212</v>
+        <v>35</v>
       </c>
       <c r="F97" t="s">
-        <v>185</v>
+        <v>37</v>
       </c>
       <c r="I97" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J97" s="2">
-        <v>46331.496527777781</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K97" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L97" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4435,34 +4411,25 @@
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>25</v>
-      </c>
-      <c r="C98" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D98" t="s">
-        <v>204</v>
-      </c>
-      <c r="E98" s="1">
-        <v>1</v>
+        <v>208</v>
       </c>
       <c r="F98" t="s">
-        <v>23</v>
-      </c>
-      <c r="G98" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="I98" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J98" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.375</v>
       </c>
       <c r="K98" s="2">
-        <v>46332.75</v>
+        <v>46333.5</v>
       </c>
       <c r="L98" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4470,214 +4437,54 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>20</v>
-      </c>
-      <c r="C99" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D99" t="s">
-        <v>206</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F99" t="s">
-        <v>88</v>
-      </c>
-      <c r="G99" t="s">
-        <v>17</v>
-      </c>
-      <c r="H99" t="s">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="I99" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J99" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.375</v>
       </c>
       <c r="K99" s="2">
-        <v>46332.75</v>
+        <v>46333.5</v>
       </c>
       <c r="L99" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B100" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="C100" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="D100" t="s">
-        <v>205</v>
-      </c>
-      <c r="E100" s="1">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="F100" t="s">
-        <v>23</v>
-      </c>
-      <c r="G100" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="I100" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J100" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.541666666664</v>
       </c>
       <c r="K100" s="2">
-        <v>46332.75</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="L100" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12">
-      <c r="A101" t="s">
-        <v>30</v>
-      </c>
-      <c r="B101" t="s">
-        <v>31</v>
-      </c>
-      <c r="C101" t="s">
-        <v>128</v>
-      </c>
-      <c r="D101" t="s">
-        <v>213</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="F101" t="s">
-        <v>40</v>
-      </c>
-      <c r="I101" t="s">
-        <v>18</v>
-      </c>
-      <c r="J101" s="2">
-        <v>46332.056250000001</v>
-      </c>
-      <c r="K101" s="2">
-        <v>46332.597916666666</v>
-      </c>
-      <c r="L101" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12">
-      <c r="A102" t="s">
-        <v>12</v>
-      </c>
-      <c r="B102" t="s">
-        <v>50</v>
-      </c>
-      <c r="C102" t="s">
-        <v>51</v>
-      </c>
-      <c r="D102" t="s">
-        <v>52</v>
-      </c>
-      <c r="F102" t="s">
-        <v>54</v>
-      </c>
-      <c r="I102" t="s">
-        <v>18</v>
-      </c>
-      <c r="J102" s="2">
-        <v>46332.291666666664</v>
-      </c>
-      <c r="K102" s="2">
-        <v>46332.791666666664</v>
-      </c>
-      <c r="L102" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12">
-      <c r="A103" t="s">
-        <v>30</v>
-      </c>
-      <c r="B103" t="s">
-        <v>31</v>
-      </c>
-      <c r="D103" t="s">
-        <v>215</v>
-      </c>
-      <c r="F103" t="s">
-        <v>95</v>
-      </c>
-      <c r="I103" t="s">
-        <v>18</v>
-      </c>
-      <c r="J103" s="2">
-        <v>46332.375</v>
-      </c>
-      <c r="K103" s="2">
-        <v>46333.5</v>
-      </c>
-      <c r="L103" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12">
-      <c r="A104" t="s">
-        <v>30</v>
-      </c>
-      <c r="B104" t="s">
-        <v>31</v>
-      </c>
-      <c r="D104" t="s">
-        <v>215</v>
-      </c>
-      <c r="F104" t="s">
-        <v>95</v>
-      </c>
-      <c r="I104" t="s">
-        <v>18</v>
-      </c>
-      <c r="J104" s="2">
-        <v>46332.375</v>
-      </c>
-      <c r="K104" s="2">
-        <v>46333.5</v>
-      </c>
-      <c r="L104" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12">
-      <c r="A105" t="s">
-        <v>12</v>
-      </c>
-      <c r="B105" t="s">
-        <v>67</v>
-      </c>
-      <c r="C105" t="s">
-        <v>68</v>
-      </c>
-      <c r="D105" t="s">
-        <v>69</v>
-      </c>
-      <c r="F105" t="s">
-        <v>70</v>
-      </c>
-      <c r="I105" t="s">
-        <v>18</v>
-      </c>
-      <c r="J105" s="2">
-        <v>46332.541666666664</v>
-      </c>
-      <c r="K105" s="2">
-        <v>46333.041666666664</v>
-      </c>
-      <c r="L105" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -4689,6 +4496,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -4826,7 +4639,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4835,7 +4648,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
   <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
   <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
@@ -4843,24 +4656,18 @@
 </scriptIds>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
--- a/data/vessels/2026-10-15.xlsx
+++ b/data/vessels/2026-10-15.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="427975" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C396799-6A5A-4A3B-ACD8-A5AF2CFAD9A4}"/>
+  <xr:revisionPtr revIDLastSave="428292" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39B9670A-E36C-421F-8F58-41852B19EDF1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="212">
   <si>
     <t>Harbor</t>
   </si>
@@ -101,42 +101,45 @@
     <t>Container</t>
   </si>
   <si>
+    <t>At berth</t>
+  </si>
+  <si>
+    <t>Ad Hoc</t>
+  </si>
+  <si>
+    <t>CMA CGM BYBLOS</t>
+  </si>
+  <si>
+    <t>CPN00/CPN01</t>
+  </si>
+  <si>
+    <t>CMA CGM</t>
+  </si>
+  <si>
+    <t>Norton Lilly International</t>
+  </si>
+  <si>
+    <t>Not available</t>
+  </si>
+  <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>CLX</t>
+  </si>
+  <si>
+    <t>CAPE TAINARO</t>
+  </si>
+  <si>
+    <t>MC642R</t>
+  </si>
+  <si>
+    <t>MSC</t>
+  </si>
+  <si>
     <t>In transit</t>
   </si>
   <si>
-    <t>Ad Hoc</t>
-  </si>
-  <si>
-    <t>CMA CGM BYBLOS</t>
-  </si>
-  <si>
-    <t>CPN00/CPN01</t>
-  </si>
-  <si>
-    <t>CMA CGM</t>
-  </si>
-  <si>
-    <t>Norton Lilly International</t>
-  </si>
-  <si>
-    <t>Not available</t>
-  </si>
-  <si>
-    <t>T5</t>
-  </si>
-  <si>
-    <t>CLX</t>
-  </si>
-  <si>
-    <t>CAPE TAINARO</t>
-  </si>
-  <si>
-    <t>MC642R</t>
-  </si>
-  <si>
-    <t>MSC</t>
-  </si>
-  <si>
     <t>Tacoma</t>
   </si>
   <si>
@@ -182,6 +185,24 @@
     <t>Ro-Ro</t>
   </si>
   <si>
+    <t>TOTE</t>
+  </si>
+  <si>
+    <t>Tote - AK2</t>
+  </si>
+  <si>
+    <t>NORTH STAR</t>
+  </si>
+  <si>
+    <t>Tote</t>
+  </si>
+  <si>
+    <t>Tote Maritime Alaska Inc</t>
+  </si>
+  <si>
+    <t>Multipurpose</t>
+  </si>
+  <si>
     <t>PNW1</t>
   </si>
   <si>
@@ -197,24 +218,6 @@
     <t>Inchcape</t>
   </si>
   <si>
-    <t>TOTE</t>
-  </si>
-  <si>
-    <t>Tote - AK2</t>
-  </si>
-  <si>
-    <t>NORTH STAR</t>
-  </si>
-  <si>
-    <t>Tote</t>
-  </si>
-  <si>
-    <t>Tote Maritime Alaska Inc</t>
-  </si>
-  <si>
-    <t>Multipurpose</t>
-  </si>
-  <si>
     <t>EB1</t>
   </si>
   <si>
@@ -350,6 +353,12 @@
     <t>643S</t>
   </si>
   <si>
+    <t>Tote - AK1</t>
+  </si>
+  <si>
+    <t>MIDNIGHT SUN</t>
+  </si>
+  <si>
     <t>VIENNA EXPRESS</t>
   </si>
   <si>
@@ -359,12 +368,6 @@
     <t>Hapag-Lloyd</t>
   </si>
   <si>
-    <t>Tote - AK1</t>
-  </si>
-  <si>
-    <t>MIDNIGHT SUN</t>
-  </si>
-  <si>
     <t>EVER MACH</t>
   </si>
   <si>
@@ -446,6 +449,18 @@
     <t>ARC</t>
   </si>
   <si>
+    <t>LIBERTY PEACE</t>
+  </si>
+  <si>
+    <t>086S</t>
+  </si>
+  <si>
+    <t>Liberty</t>
+  </si>
+  <si>
+    <t>Pacific Terminals</t>
+  </si>
+  <si>
     <t>EXPRESS ROME</t>
   </si>
   <si>
@@ -494,12 +509,6 @@
     <t>LIBERTY PASSION</t>
   </si>
   <si>
-    <t>Liberty</t>
-  </si>
-  <si>
-    <t>Pacific Terminals</t>
-  </si>
-  <si>
     <t>FRANKFURT EXPRESS</t>
   </si>
   <si>
@@ -545,28 +554,28 @@
     <t>FP22632C</t>
   </si>
   <si>
+    <t>MSC SOLA</t>
+  </si>
+  <si>
+    <t>UK639A</t>
+  </si>
+  <si>
     <t>ONE DURBAN</t>
   </si>
   <si>
     <t>NBBT0001E</t>
   </si>
   <si>
-    <t>MSC SOLA</t>
-  </si>
-  <si>
-    <t>UK639A</t>
+    <t>MORNING LUCY</t>
+  </si>
+  <si>
+    <t>KW665</t>
   </si>
   <si>
     <t>LAVENDER ACE</t>
   </si>
   <si>
     <t>123A</t>
-  </si>
-  <si>
-    <t>MORNING LUCY</t>
-  </si>
-  <si>
-    <t>KW665</t>
   </si>
   <si>
     <t>HYUNDAI FORWARD</t>
@@ -738,10 +747,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L100" totalsRowShown="0">
-  <autoFilter ref="A1:L100" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L100">
-    <sortCondition ref="J2:J100"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L101" totalsRowShown="0">
+  <autoFilter ref="A1:L101" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L101">
+    <sortCondition ref="J2:J101"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1078,7 +1087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1232,33 +1241,33 @@
         <v>46312.291666666664</v>
       </c>
       <c r="L4" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I5" t="s">
         <v>19</v>
@@ -1270,30 +1279,30 @@
         <v>46311.916666666664</v>
       </c>
       <c r="L5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I6" t="s">
         <v>19</v>
@@ -1305,36 +1314,36 @@
         <v>46312.125</v>
       </c>
       <c r="L6" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
         <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G7" t="s">
         <v>25</v>
       </c>
       <c r="H7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J7" s="2">
         <v>46311.541666666664</v>
@@ -1348,78 +1357,78 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="E8" s="1">
+        <v>26164</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H8" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="I8" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J8" s="2">
         <v>46311.625</v>
       </c>
       <c r="K8" s="2">
-        <v>46312.708333333336</v>
+        <v>46312.041666666664</v>
       </c>
       <c r="L8" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="1">
-        <v>26164</v>
+        <v>55</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H9" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="I9" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="J9" s="2">
         <v>46311.625</v>
       </c>
       <c r="K9" s="2">
-        <v>46312.041666666664</v>
+        <v>46312.708333333336</v>
       </c>
       <c r="L9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1430,22 +1439,22 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G10" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I10" t="s">
         <v>19</v>
@@ -1457,36 +1466,36 @@
         <v>46312.708333333336</v>
       </c>
       <c r="L10" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
         <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G11" t="s">
         <v>25</v>
       </c>
       <c r="H11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J11" s="2">
         <v>46312.125</v>
@@ -1500,22 +1509,22 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G12" t="s">
         <v>25</v>
@@ -1530,7 +1539,7 @@
         <v>46314.75</v>
       </c>
       <c r="L12" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1541,13 +1550,13 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F13" t="s">
         <v>24</v>
@@ -1565,7 +1574,7 @@
         <v>46314.791666666664</v>
       </c>
       <c r="L13" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1576,19 +1585,19 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I14" t="s">
         <v>19</v>
@@ -1600,33 +1609,33 @@
         <v>46313.75</v>
       </c>
       <c r="L14" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
         <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G15" t="s">
         <v>25</v>
       </c>
       <c r="I15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J15" s="2">
         <v>46314.25</v>
@@ -1640,28 +1649,28 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G16" t="s">
         <v>25</v>
       </c>
       <c r="I16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J16" s="2">
         <v>46314.25</v>
@@ -1675,22 +1684,22 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E17" s="1">
         <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G17" t="s">
         <v>25</v>
@@ -1705,7 +1714,7 @@
         <v>46318.75</v>
       </c>
       <c r="L17" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1716,19 +1725,19 @@
         <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G18" t="s">
         <v>25</v>
       </c>
       <c r="H18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I18" t="s">
         <v>19</v>
@@ -1740,30 +1749,30 @@
         <v>46315.166666666664</v>
       </c>
       <c r="L18" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s">
         <v>19</v>
@@ -1775,30 +1784,30 @@
         <v>46316.791666666664</v>
       </c>
       <c r="L19" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G20" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="I20" t="s">
         <v>19</v>
@@ -1810,7 +1819,7 @@
         <v>46317.166666666664</v>
       </c>
       <c r="L20" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1821,13 +1830,13 @@
         <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F21" t="s">
         <v>31</v>
@@ -1845,33 +1854,33 @@
         <v>46317.75</v>
       </c>
       <c r="L21" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
         <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G22" t="s">
         <v>25</v>
       </c>
       <c r="I22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J22" s="2">
         <v>46315.541666666664</v>
@@ -1885,28 +1894,28 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C23" t="s">
         <v>21</v>
       </c>
       <c r="D23" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E23" s="1">
         <v>63</v>
       </c>
       <c r="F23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G23" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="I23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J23" s="2">
         <v>46316.25</v>
@@ -1920,28 +1929,28 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D24" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I24" t="s">
         <v>19</v>
@@ -1953,62 +1962,65 @@
         <v>46316.916666666664</v>
       </c>
       <c r="L24" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>103</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="E25" s="1">
+        <v>26169</v>
       </c>
       <c r="F25" t="s">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="G25" t="s">
-        <v>25</v>
+        <v>52</v>
+      </c>
+      <c r="H25" t="s">
+        <v>52</v>
       </c>
       <c r="I25" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J25" s="2">
         <v>46316.625</v>
       </c>
       <c r="K25" s="2">
-        <v>46319.75</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L25" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D26" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F26" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G26" t="s">
         <v>25</v>
@@ -2023,65 +2035,62 @@
         <v>46319.75</v>
       </c>
       <c r="L26" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C27" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" t="s">
         <v>106</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E27" s="1">
-        <v>26169</v>
-      </c>
       <c r="F27" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="G27" t="s">
-        <v>56</v>
-      </c>
-      <c r="H27" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="I27" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="J27" s="2">
         <v>46316.625</v>
       </c>
       <c r="K27" s="2">
-        <v>46317.041666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L27" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I28" t="s">
         <v>19</v>
@@ -2093,7 +2102,7 @@
         <v>46318.708333333336</v>
       </c>
       <c r="L28" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2104,19 +2113,19 @@
         <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I29" t="s">
         <v>19</v>
@@ -2128,7 +2137,7 @@
         <v>46318.166666666664</v>
       </c>
       <c r="L29" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2142,10 +2151,10 @@
         <v>28</v>
       </c>
       <c r="D30" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F30" t="s">
         <v>31</v>
@@ -2160,36 +2169,36 @@
         <v>46318.166666666664</v>
       </c>
       <c r="L30" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C31" t="s">
         <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s">
         <v>25</v>
       </c>
       <c r="H31" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I31" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J31" s="2">
         <v>46317.666666666664</v>
@@ -2209,13 +2218,13 @@
         <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D32" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F32" t="s">
         <v>17</v>
@@ -2230,30 +2239,30 @@
         <v>46318.969444444447</v>
       </c>
       <c r="L32" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C33" t="s">
         <v>21</v>
       </c>
       <c r="D33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I33" t="s">
         <v>19</v>
@@ -2270,31 +2279,31 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
         <v>21</v>
       </c>
       <c r="D34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F34" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G34" t="s">
         <v>25</v>
       </c>
       <c r="H34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J34" s="2">
         <v>46318.208333333336</v>
@@ -2308,28 +2317,28 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C35" t="s">
         <v>21</v>
       </c>
       <c r="D35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F35" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G35" t="s">
         <v>25</v>
       </c>
       <c r="I35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J35" s="2">
         <v>46318.25</v>
@@ -2349,22 +2358,22 @@
         <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D36" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F36" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G36" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I36" t="s">
         <v>19</v>
@@ -2376,33 +2385,33 @@
         <v>46319.166666666664</v>
       </c>
       <c r="L36" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C37" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D37" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I37" t="s">
         <v>19</v>
@@ -2414,36 +2423,36 @@
         <v>46319.125</v>
       </c>
       <c r="L37" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C38" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E38" s="1">
         <v>26168</v>
       </c>
       <c r="F38" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G38" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H38" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I38" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J38" s="2">
         <v>46318.625</v>
@@ -2457,22 +2466,22 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C39" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D39" t="s">
+        <v>130</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="F39" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I39" t="s">
         <v>19</v>
@@ -2484,33 +2493,33 @@
         <v>46319.204861111109</v>
       </c>
       <c r="L39" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C40" t="s">
         <v>21</v>
       </c>
       <c r="D40" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E40" s="1">
         <v>4</v>
       </c>
       <c r="F40" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G40" t="s">
         <v>25</v>
       </c>
       <c r="I40" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J40" s="2">
         <v>46319.208333333336</v>
@@ -2524,28 +2533,28 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C41" t="s">
         <v>21</v>
       </c>
       <c r="D41" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G41" t="s">
         <v>25</v>
       </c>
       <c r="I41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J41" s="2">
         <v>46319.25</v>
@@ -2559,28 +2568,28 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B42" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C42" t="s">
         <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G42" t="s">
         <v>25</v>
       </c>
       <c r="I42" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J42" s="2">
         <v>46319.25</v>
@@ -2594,37 +2603,40 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="C43" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="D43" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F43" t="s">
-        <v>31</v>
+        <v>138</v>
       </c>
       <c r="G43" t="s">
-        <v>25</v>
+        <v>58</v>
+      </c>
+      <c r="H43" t="s">
+        <v>139</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="J43" s="2">
-        <v>46319.291666666664</v>
+        <v>46319.25</v>
       </c>
       <c r="K43" s="2">
-        <v>46320.75</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L43" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2632,482 +2644,485 @@
         <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="C44" t="s">
+        <v>95</v>
       </c>
       <c r="D44" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="F44" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="G44" t="s">
         <v>25</v>
       </c>
-      <c r="H44" t="s">
-        <v>38</v>
-      </c>
       <c r="I44" t="s">
         <v>19</v>
       </c>
       <c r="J44" s="2">
-        <v>46319.625</v>
+        <v>46319.291666666664</v>
       </c>
       <c r="K44" s="2">
-        <v>46320.166666666664</v>
+        <v>46320.75</v>
       </c>
       <c r="L44" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" t="s">
+        <v>142</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F45" t="s">
         <v>83</v>
       </c>
-      <c r="C45" t="s">
-        <v>84</v>
-      </c>
-      <c r="D45" t="s">
-        <v>138</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F45" t="s">
-        <v>87</v>
+      <c r="G45" t="s">
+        <v>25</v>
+      </c>
+      <c r="H45" t="s">
+        <v>39</v>
       </c>
       <c r="I45" t="s">
         <v>19</v>
       </c>
       <c r="J45" s="2">
-        <v>46320</v>
+        <v>46319.625</v>
       </c>
       <c r="K45" s="2">
-        <v>46322</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L45" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="C46" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="D46" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F46" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="I46" t="s">
         <v>19</v>
       </c>
       <c r="J46" s="2">
-        <v>46320.21875</v>
+        <v>46320</v>
       </c>
       <c r="K46" s="2">
-        <v>46324.59375</v>
+        <v>46322</v>
       </c>
       <c r="L46" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>142</v>
+        <v>65</v>
       </c>
       <c r="D47" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F47" t="s">
-        <v>93</v>
-      </c>
-      <c r="G47" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="I47" t="s">
         <v>19</v>
       </c>
       <c r="J47" s="2">
-        <v>46321.208333333336</v>
+        <v>46320.21875</v>
       </c>
       <c r="K47" s="2">
-        <v>46323.166666666664</v>
+        <v>46324.59375</v>
       </c>
       <c r="L47" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B48" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="C48" t="s">
+        <v>147</v>
+      </c>
+      <c r="D48" t="s">
+        <v>148</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F48" t="s">
         <v>94</v>
       </c>
-      <c r="D48" t="s">
-        <v>145</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F48" t="s">
-        <v>31</v>
+      <c r="G48" t="s">
+        <v>58</v>
       </c>
       <c r="I48" t="s">
         <v>19</v>
       </c>
       <c r="J48" s="2">
-        <v>46321.21875</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K48" s="2">
-        <v>46323.21875</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L48" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="C49" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D49" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F49" t="s">
-        <v>93</v>
-      </c>
-      <c r="G49" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="I49" t="s">
         <v>19</v>
       </c>
       <c r="J49" s="2">
-        <v>46321.25</v>
+        <v>46321.21875</v>
       </c>
       <c r="K49" s="2">
-        <v>46323.166666666664</v>
+        <v>46323.21875</v>
       </c>
       <c r="L49" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B50" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="C50" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D50" t="s">
-        <v>149</v>
-      </c>
-      <c r="E50" s="1">
-        <v>21</v>
+        <v>152</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="F50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G50" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="I50" t="s">
         <v>19</v>
       </c>
       <c r="J50" s="2">
-        <v>46321.625</v>
+        <v>46321.25</v>
       </c>
       <c r="K50" s="2">
-        <v>46325.75</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L50" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B51" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C51" t="s">
+        <v>79</v>
+      </c>
+      <c r="D51" t="s">
+        <v>154</v>
+      </c>
+      <c r="E51" s="1">
         <v>21</v>
       </c>
-      <c r="D51" t="s">
-        <v>150</v>
-      </c>
       <c r="F51" t="s">
-        <v>151</v>
+        <v>94</v>
       </c>
       <c r="G51" t="s">
-        <v>51</v>
-      </c>
-      <c r="H51" t="s">
-        <v>152</v>
+        <v>25</v>
       </c>
       <c r="I51" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J51" s="2">
-        <v>46322.25</v>
+        <v>46321.625</v>
       </c>
       <c r="K51" s="2">
-        <v>46322.75</v>
+        <v>46325.75</v>
       </c>
       <c r="L51" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C52" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="D52" t="s">
-        <v>153</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F52" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="G52" t="s">
-        <v>25</v>
+        <v>58</v>
+      </c>
+      <c r="H52" t="s">
+        <v>139</v>
       </c>
       <c r="I52" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="J52" s="2">
-        <v>46322.625</v>
+        <v>46322.25</v>
       </c>
       <c r="K52" s="2">
-        <v>46325.75</v>
+        <v>46322.75</v>
       </c>
       <c r="L52" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C53" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D53" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F53" t="s">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="G53" t="s">
         <v>25</v>
       </c>
       <c r="I53" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J53" s="2">
-        <v>46323.25</v>
+        <v>46322.625</v>
       </c>
       <c r="K53" s="2">
-        <v>46323.75</v>
+        <v>46325.75</v>
       </c>
       <c r="L53" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C54" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D54" t="s">
-        <v>35</v>
+        <v>158</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F54" t="s">
-        <v>37</v>
+        <v>46</v>
+      </c>
+      <c r="G54" t="s">
+        <v>25</v>
       </c>
       <c r="I54" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="J54" s="2">
-        <v>46323.291666666664</v>
+        <v>46323.25</v>
       </c>
       <c r="K54" s="2">
-        <v>46323.791666666664</v>
+        <v>46323.75</v>
       </c>
       <c r="L54" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B55" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C55" t="s">
-        <v>106</v>
+        <v>35</v>
       </c>
       <c r="D55" t="s">
-        <v>107</v>
-      </c>
-      <c r="E55" s="1">
-        <v>26173</v>
+        <v>36</v>
       </c>
       <c r="F55" t="s">
-        <v>55</v>
-      </c>
-      <c r="G55" t="s">
-        <v>56</v>
-      </c>
-      <c r="H55" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I55" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="J55" s="2">
-        <v>46323.625</v>
+        <v>46323.291666666664</v>
       </c>
       <c r="K55" s="2">
-        <v>46324.041666666664</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="L55" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B56" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C56" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="D56" t="s">
-        <v>155</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>156</v>
+        <v>105</v>
+      </c>
+      <c r="E56" s="1">
+        <v>26173</v>
       </c>
       <c r="F56" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G56" t="s">
-        <v>25</v>
+        <v>52</v>
+      </c>
+      <c r="H56" t="s">
+        <v>52</v>
       </c>
       <c r="I56" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="J56" s="2">
-        <v>46323.791666666664</v>
+        <v>46323.625</v>
       </c>
       <c r="K56" s="2">
-        <v>46324.75</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L56" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B57" t="s">
-        <v>83</v>
+        <v>43</v>
+      </c>
+      <c r="C57" t="s">
+        <v>21</v>
       </c>
       <c r="D57" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F57" t="s">
-        <v>87</v>
+        <v>46</v>
+      </c>
+      <c r="G57" t="s">
+        <v>25</v>
       </c>
       <c r="I57" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="J57" s="2">
-        <v>46324</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K57" s="2">
-        <v>46326</v>
+        <v>46324.75</v>
       </c>
       <c r="L57" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B58" t="s">
-        <v>13</v>
-      </c>
-      <c r="C58" t="s">
-        <v>159</v>
+        <v>84</v>
       </c>
       <c r="D58" t="s">
         <v>160</v>
@@ -3116,19 +3131,19 @@
         <v>161</v>
       </c>
       <c r="F58" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="I58" t="s">
         <v>19</v>
       </c>
       <c r="J58" s="2">
-        <v>46324.647916666669</v>
+        <v>46324</v>
       </c>
       <c r="K58" s="2">
-        <v>46326.147916666669</v>
+        <v>46326</v>
       </c>
       <c r="L58" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3136,31 +3151,31 @@
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>28</v>
+        <v>162</v>
       </c>
       <c r="D59" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F59" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I59" t="s">
         <v>19</v>
       </c>
       <c r="J59" s="2">
-        <v>46325.003472222219</v>
+        <v>46324.647916666669</v>
       </c>
       <c r="K59" s="2">
-        <v>46325.878472222219</v>
+        <v>46326.147916666669</v>
       </c>
       <c r="L59" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3168,150 +3183,150 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C60" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D60" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F60" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I60" t="s">
         <v>19</v>
       </c>
       <c r="J60" s="2">
-        <v>46325.056944444441</v>
+        <v>46325.003472222219</v>
       </c>
       <c r="K60" s="2">
-        <v>46326.098611111112</v>
+        <v>46325.878472222219</v>
       </c>
       <c r="L60" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>101</v>
+        <v>167</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>168</v>
       </c>
       <c r="F61" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="I61" t="s">
         <v>19</v>
       </c>
       <c r="J61" s="2">
-        <v>46325.333333333336</v>
+        <v>46325.056944444441</v>
       </c>
       <c r="K61" s="2">
-        <v>46325.833333333336</v>
+        <v>46326.098611111112</v>
       </c>
       <c r="L61" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B62" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C62" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="D62" t="s">
-        <v>54</v>
-      </c>
-      <c r="E62" s="1">
-        <v>26172</v>
+        <v>102</v>
       </c>
       <c r="F62" t="s">
-        <v>55</v>
-      </c>
-      <c r="G62" t="s">
-        <v>56</v>
-      </c>
-      <c r="H62" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I62" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="J62" s="2">
-        <v>46325.625</v>
+        <v>46325.333333333336</v>
       </c>
       <c r="K62" s="2">
-        <v>46326.041666666664</v>
+        <v>46325.833333333336</v>
       </c>
       <c r="L62" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B63" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C63" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>166</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>167</v>
+        <v>50</v>
+      </c>
+      <c r="E63" s="1">
+        <v>26172</v>
       </c>
       <c r="F63" t="s">
-        <v>45</v>
+        <v>51</v>
+      </c>
+      <c r="G63" t="s">
+        <v>52</v>
+      </c>
+      <c r="H63" t="s">
+        <v>52</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J63" s="2">
         <v>46325.625</v>
       </c>
       <c r="K63" s="2">
-        <v>46329.708333333336</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L63" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C64" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D64" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F64" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I64" t="s">
         <v>19</v>
@@ -3323,39 +3338,39 @@
         <v>46329.708333333336</v>
       </c>
       <c r="L64" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B65" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="C65" t="s">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="D65" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F65" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I65" t="s">
         <v>19</v>
       </c>
       <c r="J65" s="2">
-        <v>46326.166666666664</v>
+        <v>46325.625</v>
       </c>
       <c r="K65" s="2">
-        <v>46328.916666666664</v>
+        <v>46329.708333333336</v>
       </c>
       <c r="L65" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3366,13 +3381,13 @@
         <v>27</v>
       </c>
       <c r="C66" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D66" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F66" t="s">
         <v>31</v>
@@ -3387,68 +3402,65 @@
         <v>46328.125</v>
       </c>
       <c r="L66" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B67" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="C67" t="s">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="D67" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F67" t="s">
-        <v>45</v>
-      </c>
-      <c r="G67" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="I67" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J67" s="2">
-        <v>46326.25</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K67" s="2">
-        <v>46326.75</v>
+        <v>46328.916666666664</v>
       </c>
       <c r="L67" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B68" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C68" t="s">
         <v>21</v>
       </c>
       <c r="D68" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F68" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G68" t="s">
         <v>25</v>
       </c>
       <c r="I68" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J68" s="2">
         <v>46326.25</v>
@@ -3462,409 +3474,412 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B69" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C69" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D69" t="s">
-        <v>41</v>
+        <v>177</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="F69" t="s">
-        <v>37</v>
+        <v>46</v>
+      </c>
+      <c r="G69" t="s">
+        <v>25</v>
       </c>
       <c r="I69" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="J69" s="2">
-        <v>46326.416666666664</v>
+        <v>46326.25</v>
       </c>
       <c r="K69" s="2">
         <v>46326.75</v>
       </c>
       <c r="L69" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B70" t="s">
+        <v>34</v>
+      </c>
+      <c r="C70" t="s">
+        <v>41</v>
+      </c>
+      <c r="D70" t="s">
         <v>42</v>
       </c>
-      <c r="C70" t="s">
-        <v>21</v>
-      </c>
-      <c r="D70" t="s">
-        <v>174</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="F70" t="s">
-        <v>74</v>
-      </c>
-      <c r="G70" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="I70" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J70" s="2">
-        <v>46326.791666666664</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K70" s="2">
-        <v>46327.75</v>
+        <v>46326.75</v>
       </c>
       <c r="L70" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B71" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="C71" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="D71" t="s">
+        <v>175</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="F71" t="s">
-        <v>178</v>
+        <v>75</v>
+      </c>
+      <c r="G71" t="s">
+        <v>25</v>
       </c>
       <c r="I71" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="J71" s="2">
-        <v>46326.833333333336</v>
+        <v>46326.791666666664</v>
       </c>
       <c r="K71" s="2">
-        <v>46329.583333333336</v>
+        <v>46327.75</v>
       </c>
       <c r="L71" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="C72" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="D72" t="s">
         <v>179</v>
       </c>
-      <c r="E72" s="1">
-        <v>69</v>
+      <c r="E72" s="1" t="s">
+        <v>180</v>
       </c>
       <c r="F72" t="s">
-        <v>24</v>
+        <v>181</v>
       </c>
       <c r="I72" t="s">
         <v>19</v>
       </c>
       <c r="J72" s="2">
-        <v>46327.166666666664</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K72" s="2">
-        <v>46328.541666666664</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L72" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="D73" t="s">
-        <v>180</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
+      </c>
+      <c r="E73" s="1">
+        <v>69</v>
       </c>
       <c r="F73" t="s">
-        <v>45</v>
-      </c>
-      <c r="G73" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I73" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J73" s="2">
-        <v>46327.25</v>
+        <v>46327.166666666664</v>
       </c>
       <c r="K73" s="2">
-        <v>46327.708333333336</v>
+        <v>46328.541666666664</v>
       </c>
       <c r="L73" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>43</v>
+      </c>
+      <c r="C74" t="s">
+        <v>21</v>
       </c>
       <c r="D74" t="s">
-        <v>182</v>
+        <v>183</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="F74" t="s">
-        <v>82</v>
+        <v>46</v>
+      </c>
+      <c r="G74" t="s">
+        <v>25</v>
       </c>
       <c r="I74" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="J74" s="2">
+        <v>46327.25</v>
+      </c>
+      <c r="K74" s="2">
         <v>46327.708333333336</v>
       </c>
-      <c r="K74" s="2">
-        <v>46328.833333333336</v>
-      </c>
       <c r="L74" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>89</v>
-      </c>
-      <c r="C75" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="D75" t="s">
-        <v>183</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F75" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="I75" t="s">
         <v>19</v>
       </c>
       <c r="J75" s="2">
-        <v>46327.904861111114</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K75" s="2">
-        <v>46331.196527777778</v>
+        <v>46328.833333333336</v>
       </c>
       <c r="L75" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B76" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C76" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F76" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="I76" t="s">
         <v>19</v>
       </c>
       <c r="J76" s="2">
-        <v>46329</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K76" s="2">
-        <v>46330</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L76" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B77" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="C77" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="D77" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F77" t="s">
-        <v>45</v>
-      </c>
-      <c r="G77" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="I77" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J77" s="2">
-        <v>46329.25</v>
+        <v>46329</v>
       </c>
       <c r="K77" s="2">
-        <v>46329.75</v>
+        <v>46330</v>
       </c>
       <c r="L77" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B78" t="s">
         <v>59</v>
       </c>
       <c r="C78" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="D78" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F78" t="s">
-        <v>178</v>
+        <v>46</v>
+      </c>
+      <c r="G78" t="s">
+        <v>25</v>
       </c>
       <c r="I78" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="J78" s="2">
-        <v>46329.333333333336</v>
+        <v>46329.25</v>
       </c>
       <c r="K78" s="2">
-        <v>46332.625</v>
+        <v>46329.75</v>
       </c>
       <c r="L78" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B79" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C79" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D79" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F79" t="s">
-        <v>45</v>
-      </c>
-      <c r="G79" t="s">
-        <v>25</v>
+        <v>181</v>
       </c>
       <c r="I79" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J79" s="2">
-        <v>46329.791666666664</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K79" s="2">
-        <v>46330.75</v>
+        <v>46332.625</v>
       </c>
       <c r="L79" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B80" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C80" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="D80" t="s">
+        <v>190</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="F80" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="G80" t="s">
+        <v>25</v>
       </c>
       <c r="I80" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="J80" s="2">
-        <v>46330.208333333336</v>
+        <v>46329.791666666664</v>
       </c>
       <c r="K80" s="2">
-        <v>46334</v>
+        <v>46330.75</v>
       </c>
       <c r="L80" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B81" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C81" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D81" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F81" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I81" t="s">
         <v>19</v>
@@ -3876,88 +3891,88 @@
         <v>46334</v>
       </c>
       <c r="L81" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B82" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C82" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="D82" t="s">
-        <v>107</v>
+        <v>194</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="F82" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I82" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="J82" s="2">
-        <v>46330.625</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K82" s="2">
-        <v>46331.125</v>
+        <v>46334</v>
       </c>
       <c r="L82" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B83" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C83" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="D83" t="s">
-        <v>193</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>194</v>
+        <v>105</v>
       </c>
       <c r="F83" t="s">
-        <v>178</v>
+        <v>51</v>
       </c>
       <c r="I83" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J83" s="2">
-        <v>46330.633333333331</v>
+        <v>46330.625</v>
       </c>
       <c r="K83" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.125</v>
       </c>
       <c r="L83" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B84" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C84" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D84" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F84" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="I84" t="s">
         <v>19</v>
@@ -3969,114 +3984,108 @@
         <v>46333.925000000003</v>
       </c>
       <c r="L84" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B85" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="C85" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D85" t="s">
-        <v>129</v>
+        <v>196</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>197</v>
       </c>
       <c r="F85" t="s">
-        <v>37</v>
+        <v>181</v>
       </c>
       <c r="I85" t="s">
         <v>19</v>
       </c>
       <c r="J85" s="2">
-        <v>46330.704861111109</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K85" s="2">
-        <v>46331.204861111109</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L85" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B86" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C86" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="D86" t="s">
-        <v>195</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>196</v>
+        <v>130</v>
       </c>
       <c r="F86" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="I86" t="s">
         <v>19</v>
       </c>
       <c r="J86" s="2">
-        <v>46330.75</v>
+        <v>46330.704861111109</v>
       </c>
       <c r="K86" s="2">
-        <v>46332.75</v>
+        <v>46331.204861111109</v>
       </c>
       <c r="L86" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C87" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="D87" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F87" t="s">
-        <v>74</v>
-      </c>
-      <c r="G87" t="s">
-        <v>25</v>
-      </c>
-      <c r="H87" t="s">
-        <v>199</v>
+        <v>31</v>
       </c>
       <c r="I87" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J87" s="2">
-        <v>46331.25</v>
+        <v>46330.75</v>
       </c>
       <c r="K87" s="2">
-        <v>46331.75</v>
+        <v>46332.75</v>
       </c>
       <c r="L87" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B88" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C88" t="s">
         <v>21</v>
@@ -4084,17 +4093,20 @@
       <c r="D88" t="s">
         <v>200</v>
       </c>
-      <c r="E88" s="1">
-        <v>10</v>
+      <c r="E88" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="F88" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="G88" t="s">
         <v>25</v>
       </c>
+      <c r="H88" t="s">
+        <v>202</v>
+      </c>
       <c r="I88" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J88" s="2">
         <v>46331.25</v>
@@ -4108,28 +4120,28 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B89" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C89" t="s">
         <v>21</v>
       </c>
       <c r="D89" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E89" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F89" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G89" t="s">
         <v>25</v>
       </c>
       <c r="I89" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J89" s="2">
         <v>46331.25</v>
@@ -4143,86 +4155,89 @@
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B90" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C90" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D90" t="s">
-        <v>202</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
+      </c>
+      <c r="E90" s="1">
+        <v>1</v>
       </c>
       <c r="F90" t="s">
-        <v>31</v>
+        <v>99</v>
+      </c>
+      <c r="G90" t="s">
+        <v>25</v>
       </c>
       <c r="I90" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="J90" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.25</v>
       </c>
       <c r="K90" s="2">
-        <v>46332.166666666664</v>
+        <v>46331.75</v>
       </c>
       <c r="L90" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="C91" t="s">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="D91" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F91" t="s">
-        <v>178</v>
+        <v>31</v>
       </c>
       <c r="I91" t="s">
         <v>19</v>
       </c>
       <c r="J91" s="2">
-        <v>46331.496527777781</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K91" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L91" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B92" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C92" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D92" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F92" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="I92" t="s">
         <v>19</v>
@@ -4234,71 +4249,65 @@
         <v>46334.746527777781</v>
       </c>
       <c r="L92" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B93" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="C93" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="D93" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="F93" t="s">
-        <v>74</v>
-      </c>
-      <c r="G93" t="s">
-        <v>25</v>
-      </c>
-      <c r="H93" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="I93" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J93" s="2">
-        <v>46331.791666666664</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K93" s="2">
-        <v>46332.75</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L93" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B94" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C94" t="s">
         <v>21</v>
       </c>
       <c r="D94" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E94" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G94" t="s">
         <v>25</v>
       </c>
       <c r="I94" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J94" s="2">
         <v>46331.791666666664</v>
@@ -4312,28 +4321,31 @@
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B95" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C95" t="s">
         <v>21</v>
       </c>
       <c r="D95" t="s">
+        <v>200</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E95" s="1">
-        <v>1</v>
-      </c>
       <c r="F95" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="G95" t="s">
         <v>25</v>
       </c>
+      <c r="H95" t="s">
+        <v>202</v>
+      </c>
       <c r="I95" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J95" s="2">
         <v>46331.791666666664</v>
@@ -4347,89 +4359,98 @@
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B96" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C96" t="s">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="D96" t="s">
-        <v>206</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
+      </c>
+      <c r="E96" s="1">
+        <v>10</v>
       </c>
       <c r="F96" t="s">
-        <v>17</v>
+        <v>99</v>
+      </c>
+      <c r="G96" t="s">
+        <v>25</v>
       </c>
       <c r="I96" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="J96" s="2">
-        <v>46332.056250000001</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K96" s="2">
-        <v>46332.597916666666</v>
+        <v>46332.75</v>
       </c>
       <c r="L96" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="D97" t="s">
-        <v>35</v>
+        <v>209</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="F97" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="I97" t="s">
         <v>19</v>
       </c>
       <c r="J97" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K97" s="2">
-        <v>46332.791666666664</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L97" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B98" t="s">
-        <v>13</v>
+        <v>34</v>
+      </c>
+      <c r="C98" t="s">
+        <v>35</v>
       </c>
       <c r="D98" t="s">
-        <v>208</v>
+        <v>36</v>
       </c>
       <c r="F98" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="I98" t="s">
         <v>19</v>
       </c>
       <c r="J98" s="2">
-        <v>46332.375</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K98" s="2">
-        <v>46333.5</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L98" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4440,10 +4461,10 @@
         <v>13</v>
       </c>
       <c r="D99" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F99" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I99" t="s">
         <v>19</v>
@@ -4455,35 +4476,61 @@
         <v>46333.5</v>
       </c>
       <c r="L99" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>52</v>
-      </c>
-      <c r="C100" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="D100" t="s">
-        <v>54</v>
+        <v>211</v>
       </c>
       <c r="F100" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="I100" t="s">
         <v>19</v>
       </c>
       <c r="J100" s="2">
+        <v>46332.375</v>
+      </c>
+      <c r="K100" s="2">
+        <v>46333.5</v>
+      </c>
+      <c r="L100" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12">
+      <c r="A101" t="s">
+        <v>33</v>
+      </c>
+      <c r="B101" t="s">
+        <v>48</v>
+      </c>
+      <c r="C101" t="s">
+        <v>49</v>
+      </c>
+      <c r="D101" t="s">
+        <v>50</v>
+      </c>
+      <c r="F101" t="s">
+        <v>51</v>
+      </c>
+      <c r="I101" t="s">
+        <v>19</v>
+      </c>
+      <c r="J101" s="2">
         <v>46332.541666666664</v>
       </c>
-      <c r="K100" s="2">
+      <c r="K101" s="2">
         <v>46333.041666666664</v>
       </c>
-      <c r="L100" t="s">
+      <c r="L101" t="s">
         <v>26</v>
       </c>
     </row>
@@ -4496,12 +4543,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
+  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
+</scriptIds>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -4639,7 +4694,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4648,26 +4703,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
-  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
-</scriptIds>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
--- a/data/vessels/2026-10-15.xlsx
+++ b/data/vessels/2026-10-15.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="428292" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39B9670A-E36C-421F-8F58-41852B19EDF1}"/>
+  <xr:revisionPtr revIDLastSave="428616" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A79A3AF-0B5D-4F6E-B124-9175B67ACE3A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -161,7 +161,7 @@
     <t>SSA Marine</t>
   </si>
   <si>
-    <t>Waiting 3.2 days</t>
+    <t>Waiting 3.4 days</t>
   </si>
   <si>
     <t>Matson - HI2</t>
@@ -185,6 +185,21 @@
     <t>Ro-Ro</t>
   </si>
   <si>
+    <t>PNW1</t>
+  </si>
+  <si>
+    <t>OOCL NEW YORK</t>
+  </si>
+  <si>
+    <t>122E/122W</t>
+  </si>
+  <si>
+    <t>OOCL</t>
+  </si>
+  <si>
+    <t>Inchcape</t>
+  </si>
+  <si>
     <t>TOTE</t>
   </si>
   <si>
@@ -203,21 +218,6 @@
     <t>Multipurpose</t>
   </si>
   <si>
-    <t>PNW1</t>
-  </si>
-  <si>
-    <t>OOCL NEW YORK</t>
-  </si>
-  <si>
-    <t>122E/122W</t>
-  </si>
-  <si>
-    <t>OOCL</t>
-  </si>
-  <si>
-    <t>Inchcape</t>
-  </si>
-  <si>
     <t>EB1</t>
   </si>
   <si>
@@ -353,21 +353,21 @@
     <t>643S</t>
   </si>
   <si>
+    <t>VIENNA EXPRESS</t>
+  </si>
+  <si>
+    <t>638E/641W</t>
+  </si>
+  <si>
+    <t>Hapag-Lloyd</t>
+  </si>
+  <si>
     <t>Tote - AK1</t>
   </si>
   <si>
     <t>MIDNIGHT SUN</t>
   </si>
   <si>
-    <t>VIENNA EXPRESS</t>
-  </si>
-  <si>
-    <t>638E/641W</t>
-  </si>
-  <si>
-    <t>Hapag-Lloyd</t>
-  </si>
-  <si>
     <t>EVER MACH</t>
   </si>
   <si>
@@ -437,30 +437,30 @@
     <t>POLARIS MILA</t>
   </si>
   <si>
+    <t>LIBERTY PEACE</t>
+  </si>
+  <si>
+    <t>086S</t>
+  </si>
+  <si>
+    <t>Liberty</t>
+  </si>
+  <si>
+    <t>Pacific Terminals</t>
+  </si>
+  <si>
+    <t>ARC INDEPENDENCE</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
     <t>ARC HONOR</t>
   </si>
   <si>
     <t>ED616</t>
   </si>
   <si>
-    <t>ARC INDEPENDENCE</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>LIBERTY PEACE</t>
-  </si>
-  <si>
-    <t>086S</t>
-  </si>
-  <si>
-    <t>Liberty</t>
-  </si>
-  <si>
-    <t>Pacific Terminals</t>
-  </si>
-  <si>
     <t>EXPRESS ROME</t>
   </si>
   <si>
@@ -650,10 +650,10 @@
     <t>Jones Stevedoring Co</t>
   </si>
   <si>
+    <t>GLOVIS LEGEND</t>
+  </si>
+  <si>
     <t>GLOVIS TREASURE</t>
-  </si>
-  <si>
-    <t>GLOVIS LEGEND</t>
   </si>
   <si>
     <t>MSC SABRINA</t>
@@ -1357,19 +1357,19 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
         <v>48</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>49</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="E8" s="1">
-        <v>26164</v>
       </c>
       <c r="F8" t="s">
         <v>51</v>
@@ -1378,27 +1378,27 @@
         <v>52</v>
       </c>
       <c r="H8" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="I8" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="J8" s="2">
         <v>46311.625</v>
       </c>
       <c r="K8" s="2">
-        <v>46312.041666666664</v>
+        <v>46312.708333333336</v>
       </c>
       <c r="L8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s">
         <v>54</v>
@@ -1406,29 +1406,29 @@
       <c r="D9" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="1">
+        <v>26164</v>
+      </c>
+      <c r="F9" t="s">
         <v>56</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>57</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9" t="s">
         <v>58</v>
-      </c>
-      <c r="H9" t="s">
-        <v>39</v>
-      </c>
-      <c r="I9" t="s">
-        <v>19</v>
       </c>
       <c r="J9" s="2">
         <v>46311.625</v>
       </c>
       <c r="K9" s="2">
-        <v>46312.708333333336</v>
+        <v>46312.041666666664</v>
       </c>
       <c r="L9" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1439,19 +1439,19 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H10" t="s">
         <v>39</v>
@@ -1807,7 +1807,7 @@
         <v>94</v>
       </c>
       <c r="G20" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I20" t="s">
         <v>19</v>
@@ -1912,7 +1912,7 @@
         <v>46</v>
       </c>
       <c r="G23" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I23" t="s">
         <v>76</v>
@@ -1970,34 +1970,31 @@
         <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" t="s">
         <v>104</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E25" s="1">
-        <v>26169</v>
-      </c>
       <c r="F25" t="s">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="G25" t="s">
-        <v>52</v>
-      </c>
-      <c r="H25" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="I25" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="J25" s="2">
         <v>46316.625</v>
       </c>
       <c r="K25" s="2">
-        <v>46317.041666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L25" t="s">
         <v>32</v>
@@ -2008,31 +2005,34 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
       <c r="D26" t="s">
-        <v>106</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="E26" s="1">
+        <v>26169</v>
       </c>
       <c r="F26" t="s">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="G26" t="s">
-        <v>25</v>
+        <v>57</v>
+      </c>
+      <c r="H26" t="s">
+        <v>57</v>
       </c>
       <c r="I26" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="J26" s="2">
         <v>46316.625</v>
       </c>
       <c r="K26" s="2">
-        <v>46319.75</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L26" t="s">
         <v>32</v>
@@ -2049,13 +2049,13 @@
         <v>61</v>
       </c>
       <c r="D27" t="s">
+        <v>104</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F27" t="s">
         <v>106</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F27" t="s">
-        <v>108</v>
       </c>
       <c r="G27" t="s">
         <v>25</v>
@@ -2358,7 +2358,7 @@
         <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D36" t="s">
         <v>126</v>
@@ -2367,10 +2367,10 @@
         <v>127</v>
       </c>
       <c r="F36" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G36" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H36" t="s">
         <v>39</v>
@@ -2431,28 +2431,28 @@
         <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E38" s="1">
         <v>26168</v>
       </c>
       <c r="F38" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G38" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H38" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I38" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="J38" s="2">
         <v>46318.625</v>
@@ -2536,7 +2536,7 @@
         <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="C41" t="s">
         <v>21</v>
@@ -2548,10 +2548,13 @@
         <v>133</v>
       </c>
       <c r="F41" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="G41" t="s">
-        <v>25</v>
+        <v>52</v>
+      </c>
+      <c r="H41" t="s">
+        <v>135</v>
       </c>
       <c r="I41" t="s">
         <v>76</v>
@@ -2560,7 +2563,7 @@
         <v>46319.25</v>
       </c>
       <c r="K41" s="2">
-        <v>46319.75</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L41" t="s">
         <v>26</v>
@@ -2577,13 +2580,13 @@
         <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G42" t="s">
         <v>25</v>
@@ -2606,25 +2609,22 @@
         <v>33</v>
       </c>
       <c r="B43" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="C43" t="s">
         <v>21</v>
       </c>
       <c r="D43" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F43" t="s">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="G43" t="s">
-        <v>58</v>
-      </c>
-      <c r="H43" t="s">
-        <v>139</v>
+        <v>25</v>
       </c>
       <c r="I43" t="s">
         <v>76</v>
@@ -2633,7 +2633,7 @@
         <v>46319.25</v>
       </c>
       <c r="K43" s="2">
-        <v>46320.166666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L43" t="s">
         <v>26</v>
@@ -2793,7 +2793,7 @@
         <v>94</v>
       </c>
       <c r="G48" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I48" t="s">
         <v>19</v>
@@ -2860,7 +2860,7 @@
         <v>94</v>
       </c>
       <c r="G50" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I50" t="s">
         <v>19</v>
@@ -2924,13 +2924,13 @@
         <v>155</v>
       </c>
       <c r="F52" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G52" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H52" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="I52" t="s">
         <v>76</v>
@@ -2962,7 +2962,7 @@
         <v>157</v>
       </c>
       <c r="F53" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G53" t="s">
         <v>25</v>
@@ -3049,28 +3049,28 @@
         <v>33</v>
       </c>
       <c r="B56" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C56" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D56" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E56" s="1">
         <v>26173</v>
       </c>
       <c r="F56" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G56" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H56" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I56" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="J56" s="2">
         <v>46323.625</v>
@@ -3276,28 +3276,28 @@
         <v>33</v>
       </c>
       <c r="B63" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C63" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D63" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E63" s="1">
         <v>26172</v>
       </c>
       <c r="F63" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G63" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H63" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I63" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="J63" s="2">
         <v>46325.625</v>
@@ -3931,19 +3931,19 @@
         <v>33</v>
       </c>
       <c r="B83" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C83" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D83" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F83" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="I83" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="J83" s="2">
         <v>46330.625</v>
@@ -4123,7 +4123,7 @@
         <v>33</v>
       </c>
       <c r="B89" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C89" t="s">
         <v>21</v>
@@ -4132,7 +4132,7 @@
         <v>203</v>
       </c>
       <c r="E89" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F89" t="s">
         <v>99</v>
@@ -4158,7 +4158,7 @@
         <v>33</v>
       </c>
       <c r="B90" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C90" t="s">
         <v>21</v>
@@ -4167,7 +4167,7 @@
         <v>204</v>
       </c>
       <c r="E90" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F90" t="s">
         <v>99</v>
@@ -4289,7 +4289,7 @@
         <v>33</v>
       </c>
       <c r="B94" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C94" t="s">
         <v>21</v>
@@ -4298,7 +4298,7 @@
         <v>204</v>
       </c>
       <c r="E94" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F94" t="s">
         <v>99</v>
@@ -4362,7 +4362,7 @@
         <v>33</v>
       </c>
       <c r="B96" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C96" t="s">
         <v>21</v>
@@ -4371,7 +4371,7 @@
         <v>203</v>
       </c>
       <c r="E96" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F96" t="s">
         <v>99</v>
@@ -4510,16 +4510,16 @@
         <v>33</v>
       </c>
       <c r="B101" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C101" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D101" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F101" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="I101" t="s">
         <v>19</v>
@@ -4543,20 +4543,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
-  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
-</scriptIds>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -4694,7 +4680,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4703,18 +4689,32 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
+  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
+</scriptIds>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>